--- a/Blockchain_Intern_Tracker.xlsx
+++ b/Blockchain_Intern_Tracker.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9000" tabRatio="500"/>
+    <workbookView windowWidth="23040" windowHeight="9000" tabRatio="500" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Tong quan" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="855" uniqueCount="449">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="854" uniqueCount="449">
   <si>
     <t>BANG THEO DOI TIEN DO - LO TRINH 12 TUAN BLOCKCHAIN DEVELOPER INTERN (RUST / SOLANA)</t>
   </si>
@@ -39,9 +39,6 @@
     <t>Ngay bat dau:</t>
   </si>
   <si>
-    <t>18/06/2026</t>
-  </si>
-  <si>
     <t>Ngay ket thuc du kien (84 ngay):</t>
   </si>
   <si>
@@ -288,19 +285,22 @@
     <t>Code MerkleTree struct, build proof, verify_proof()</t>
   </si>
   <si>
+    <t>Dang lam</t>
+  </si>
+  <si>
+    <t>Valid Anagram</t>
+  </si>
+  <si>
+    <t>Public-key cryptography, digital signature</t>
+  </si>
+  <si>
+    <t>Cloudflare - ECC primer (blog.cloudflare.com)</t>
+  </si>
+  <si>
+    <t>Dung ed25519-dalek: generate keypair, sign, verify</t>
+  </si>
+  <si>
     <t>Chua bat dau</t>
-  </si>
-  <si>
-    <t>Valid Anagram</t>
-  </si>
-  <si>
-    <t>Public-key cryptography, digital signature</t>
-  </si>
-  <si>
-    <t>Cloudflare - ECC primer (blog.cloudflare.com)</t>
-  </si>
-  <si>
-    <t>Dung ed25519-dalek: generate keypair, sign, verify</t>
   </si>
   <si>
     <t>Group Anagrams</t>
@@ -2666,27 +2666,28 @@
       <c r="A3" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="17" t="s">
-        <v>2</v>
+      <c r="B3" s="17">
+        <v>46191</v>
       </c>
       <c r="C3" s="18"/>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B4" s="19">
+        <f>B3+83</f>
         <v>46274</v>
       </c>
     </row>
     <row r="6" ht="15.6" spans="1:8">
       <c r="A6" s="6" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="8" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B7" s="20">
         <v>84</v>
@@ -2694,7 +2695,7 @@
     </row>
     <row r="8" spans="1:8">
       <c r="A8" s="8" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B8" s="20">
         <f>COUNTIF('Theo doi hang ngay'!H2:H85,"Hoan thanh")</f>
@@ -2703,16 +2704,16 @@
     </row>
     <row r="9" spans="1:8">
       <c r="A9" s="8" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B9" s="20">
         <f>COUNTIF('Theo doi hang ngay'!H2:H85,"Dang lam")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:8">
       <c r="A10" s="8" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B10" s="21">
         <f>COUNTIF('Theo doi hang ngay'!H2:H85,"Hoan thanh")/84</f>
@@ -2721,7 +2722,7 @@
     </row>
     <row r="11" spans="1:8">
       <c r="A11" s="8" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B11" s="20">
         <f>SUM('Theo doi hang ngay'!I2:I85)</f>
@@ -2730,24 +2731,24 @@
     </row>
     <row r="13" ht="15.6" spans="1:8">
       <c r="A13" s="6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="14" spans="1:8">
       <c r="A14" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B14" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B14" s="1" t="s">
+      <c r="C14" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C14" s="1" t="s">
+      <c r="D14" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D14" s="1" t="s">
+      <c r="E14" s="1" t="s">
         <v>14</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -2755,14 +2756,14 @@
         <v>1</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C15" s="11">
         <f>COUNTIFS('Theo doi hang ngay'!H2:H8,"Hoan thanh")/7</f>
         <v>0.285714285714286</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E15" s="11">
         <f>COUNTIFS('Theo doi hang ngay'!N2:N8,"Hoan thanh")/7</f>
@@ -2774,14 +2775,14 @@
         <v>2</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C16" s="11">
         <f>COUNTIFS('Theo doi hang ngay'!H9:H15,"Hoan thanh")/7</f>
         <v>0</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E16" s="11">
         <f>COUNTIFS('Theo doi hang ngay'!N9:N15,"Hoan thanh")/7</f>
@@ -2793,14 +2794,14 @@
         <v>3</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C17" s="11">
         <f>COUNTIFS('Theo doi hang ngay'!H16:H22,"Hoan thanh")/7</f>
         <v>0</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E17" s="11">
         <f>COUNTIFS('Theo doi hang ngay'!N16:N22,"Hoan thanh")/7</f>
@@ -2812,14 +2813,14 @@
         <v>4</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C18" s="11">
         <f>COUNTIFS('Theo doi hang ngay'!H23:H29,"Hoan thanh")/7</f>
         <v>0</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E18" s="11">
         <f>COUNTIFS('Theo doi hang ngay'!N23:N29,"Hoan thanh")/7</f>
@@ -2831,14 +2832,14 @@
         <v>5</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C19" s="11">
         <f>COUNTIFS('Theo doi hang ngay'!H30:H36,"Hoan thanh")/7</f>
         <v>0</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E19" s="11">
         <f>COUNTIFS('Theo doi hang ngay'!N30:N36,"Hoan thanh")/7</f>
@@ -2850,14 +2851,14 @@
         <v>6</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C20" s="11">
         <f>COUNTIFS('Theo doi hang ngay'!H37:H43,"Hoan thanh")/7</f>
         <v>0</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E20" s="11">
         <f>COUNTIFS('Theo doi hang ngay'!N37:N43,"Hoan thanh")/7</f>
@@ -2869,14 +2870,14 @@
         <v>7</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C21" s="11">
         <f>COUNTIFS('Theo doi hang ngay'!H44:H50,"Hoan thanh")/7</f>
         <v>0</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E21" s="11">
         <f>COUNTIFS('Theo doi hang ngay'!N44:N50,"Hoan thanh")/7</f>
@@ -2888,14 +2889,14 @@
         <v>8</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C22" s="11">
         <f>COUNTIFS('Theo doi hang ngay'!H51:H57,"Hoan thanh")/7</f>
         <v>0</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E22" s="11">
         <f>COUNTIFS('Theo doi hang ngay'!N51:N57,"Hoan thanh")/7</f>
@@ -2907,14 +2908,14 @@
         <v>9</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C23" s="11">
         <f>COUNTIFS('Theo doi hang ngay'!H58:H64,"Hoan thanh")/7</f>
         <v>0</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E23" s="11">
         <f>COUNTIFS('Theo doi hang ngay'!N58:N64,"Hoan thanh")/7</f>
@@ -2926,14 +2927,14 @@
         <v>10</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C24" s="11">
         <f>COUNTIFS('Theo doi hang ngay'!H65:H71,"Hoan thanh")/7</f>
         <v>0</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E24" s="11">
         <f>COUNTIFS('Theo doi hang ngay'!N65:N71,"Hoan thanh")/7</f>
@@ -2945,14 +2946,14 @@
         <v>11</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C25" s="11">
         <f>COUNTIFS('Theo doi hang ngay'!H72:H78,"Hoan thanh")/7</f>
         <v>0</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E25" s="11">
         <f>COUNTIFS('Theo doi hang ngay'!N72:N78,"Hoan thanh")/7</f>
@@ -2964,14 +2965,14 @@
         <v>12</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C26" s="11">
         <f>COUNTIFS('Theo doi hang ngay'!H79:H85,"Hoan thanh")/7</f>
         <v>0</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E26" s="11">
         <f>COUNTIFS('Theo doi hang ngay'!N79:N85,"Hoan thanh")/7</f>
@@ -2980,12 +2981,12 @@
     </row>
     <row r="28" ht="15.6" spans="1:5">
       <c r="A28" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="8" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B29" s="20">
         <v>84</v>
@@ -2993,7 +2994,7 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="8" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B30" s="20">
         <f>COUNTIF('Theo doi hang ngay'!N2:N85,"Hoan thanh")</f>
@@ -3002,16 +3003,16 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="8" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B31" s="20">
         <f>COUNTIF('Theo doi hang ngay'!N2:N85,"Dang lam")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="8" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B32" s="20">
         <f>COUNTIF('Theo doi hang ngay'!N2:N85,"Bo qua")</f>
@@ -3020,7 +3021,7 @@
     </row>
     <row r="33" spans="1:3">
       <c r="A33" s="8" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B33" s="21">
         <f>COUNTIF('Theo doi hang ngay'!N2:N85,"Hoan thanh")/84</f>
@@ -3029,23 +3030,23 @@
     </row>
     <row r="35" ht="15.6" spans="1:3">
       <c r="A35" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B36" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="B36" s="1" t="s">
+      <c r="C36" s="1" t="s">
         <v>48</v>
-      </c>
-      <c r="C36" s="1" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B37" s="3" t="str">
         <f>'Portfolio Projects'!G3</f>
@@ -3058,7 +3059,7 @@
     </row>
     <row r="38" spans="1:3">
       <c r="A38" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B38" s="3" t="str">
         <f>'Portfolio Projects'!G4</f>
@@ -3071,7 +3072,7 @@
     </row>
     <row r="39" spans="1:3">
       <c r="A39" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B39" s="3" t="str">
         <f>'Portfolio Projects'!G5</f>
@@ -3084,12 +3085,12 @@
     </row>
     <row r="41" ht="15.6" spans="1:3">
       <c r="A41" s="6" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="42" spans="1:3">
       <c r="A42" s="8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B42" s="20" t="str">
         <f>'Cau hoi phong van'!G2</f>
@@ -3136,49 +3137,49 @@
   <sheetData>
     <row r="1" ht="27.6" spans="1:15">
       <c r="A1" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>67</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="2" ht="26.4" spans="1:15">
@@ -3191,42 +3192,42 @@
       <c r="C2" s="3">
         <v>1</v>
       </c>
-      <c r="D2" s="12" t="e">
+      <c r="D2" s="12">
         <f>'Tong quan'!$B$3+(C2-1)</f>
-        <v>#VALUE!</v>
+        <v>46191</v>
       </c>
       <c r="E2" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="F2" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="G2" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="H2" s="3" t="s">
         <v>71</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>72</v>
       </c>
       <c r="I2" s="3">
         <v>1.5</v>
       </c>
       <c r="J2" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="K2" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="L2" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="K2" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="L2" s="3" t="s">
+      <c r="M2" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="M2" s="3" t="s">
+      <c r="N2" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="O2" s="3" t="s">
         <v>75</v>
-      </c>
-      <c r="N2" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="O2" s="3" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="3" ht="26.4" spans="1:15">
@@ -3239,40 +3240,40 @@
       <c r="C3" s="3">
         <v>2</v>
       </c>
-      <c r="D3" s="12" t="e">
+      <c r="D3" s="12">
         <f>'Tong quan'!$B$3+(C3-1)</f>
-        <v>#VALUE!</v>
+        <v>46192</v>
       </c>
       <c r="E3" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="F3" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="G3" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="G3" s="4" t="s">
-        <v>79</v>
-      </c>
       <c r="H3" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="I3" s="3">
         <v>2</v>
       </c>
       <c r="J3" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="K3" s="3"/>
       <c r="L3" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="M3" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="N3" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="O3" s="3" t="s">
         <v>80</v>
-      </c>
-      <c r="M3" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="N3" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="O3" s="3" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="4" ht="26.4" spans="1:15">
@@ -3285,33 +3286,33 @@
       <c r="C4" s="3">
         <v>3</v>
       </c>
-      <c r="D4" s="12" t="e">
+      <c r="D4" s="12">
         <f>'Tong quan'!$B$3+(C4-1)</f>
-        <v>#VALUE!</v>
+        <v>46193</v>
       </c>
       <c r="E4" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="F4" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="G4" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="G4" s="4" t="s">
+      <c r="H4" s="3" t="s">
         <v>84</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>85</v>
       </c>
       <c r="I4" s="3"/>
       <c r="J4" s="4"/>
       <c r="K4" s="3"/>
       <c r="L4" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="N4" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="O4" s="3"/>
     </row>
@@ -3325,21 +3326,21 @@
       <c r="C5" s="3">
         <v>4</v>
       </c>
-      <c r="D5" s="12" t="e">
+      <c r="D5" s="12">
         <f>'Tong quan'!$B$3+(C5-1)</f>
-        <v>#VALUE!</v>
+        <v>46194</v>
       </c>
       <c r="E5" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="F5" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="G5" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="G5" s="4" t="s">
-        <v>89</v>
-      </c>
       <c r="H5" s="3" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="I5" s="3"/>
       <c r="J5" s="4"/>
@@ -3351,7 +3352,7 @@
         <v>91</v>
       </c>
       <c r="N5" s="3" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="O5" s="3"/>
     </row>
@@ -3365,9 +3366,9 @@
       <c r="C6" s="3">
         <v>5</v>
       </c>
-      <c r="D6" s="12" t="e">
+      <c r="D6" s="12">
         <f>'Tong quan'!$B$3+(C6-1)</f>
-        <v>#VALUE!</v>
+        <v>46195</v>
       </c>
       <c r="E6" s="4" t="s">
         <v>92</v>
@@ -3379,7 +3380,7 @@
         <v>94</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="I6" s="3"/>
       <c r="J6" s="4"/>
@@ -3391,7 +3392,7 @@
         <v>91</v>
       </c>
       <c r="N6" s="3" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="O6" s="3"/>
     </row>
@@ -3405,9 +3406,9 @@
       <c r="C7" s="3">
         <v>6</v>
       </c>
-      <c r="D7" s="12" t="e">
+      <c r="D7" s="12">
         <f>'Tong quan'!$B$3+(C7-1)</f>
-        <v>#VALUE!</v>
+        <v>46196</v>
       </c>
       <c r="E7" s="4" t="s">
         <v>96</v>
@@ -3419,7 +3420,7 @@
         <v>98</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="I7" s="3"/>
       <c r="J7" s="4"/>
@@ -3431,7 +3432,7 @@
         <v>91</v>
       </c>
       <c r="N7" s="3" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="O7" s="3"/>
     </row>
@@ -3445,9 +3446,9 @@
       <c r="C8" s="13">
         <v>7</v>
       </c>
-      <c r="D8" s="14" t="e">
+      <c r="D8" s="14">
         <f>'Tong quan'!$B$3+(C8-1)</f>
-        <v>#VALUE!</v>
+        <v>46197</v>
       </c>
       <c r="E8" s="15" t="s">
         <v>100</v>
@@ -3459,7 +3460,7 @@
         <v>101</v>
       </c>
       <c r="H8" s="13" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="I8" s="13"/>
       <c r="J8" s="15"/>
@@ -3471,7 +3472,7 @@
         <v>91</v>
       </c>
       <c r="N8" s="13" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="O8" s="13"/>
     </row>
@@ -3485,9 +3486,9 @@
       <c r="C9" s="3">
         <v>8</v>
       </c>
-      <c r="D9" s="12" t="e">
+      <c r="D9" s="12">
         <f>'Tong quan'!$B$3+(C9-1)</f>
-        <v>#VALUE!</v>
+        <v>46198</v>
       </c>
       <c r="E9" s="4" t="s">
         <v>103</v>
@@ -3499,21 +3500,21 @@
         <v>105</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="I9" s="3"/>
       <c r="J9" s="4"/>
       <c r="K9" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="L9" s="3" t="s">
         <v>106</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="N9" s="3" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="O9" s="3"/>
     </row>
@@ -3527,9 +3528,9 @@
       <c r="C10" s="3">
         <v>9</v>
       </c>
-      <c r="D10" s="12" t="e">
+      <c r="D10" s="12">
         <f>'Tong quan'!$B$3+(C10-1)</f>
-        <v>#VALUE!</v>
+        <v>46199</v>
       </c>
       <c r="E10" s="4" t="s">
         <v>107</v>
@@ -3541,7 +3542,7 @@
         <v>109</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="I10" s="3"/>
       <c r="J10" s="4"/>
@@ -3550,10 +3551,10 @@
         <v>110</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="N10" s="3" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="O10" s="3"/>
     </row>
@@ -3567,9 +3568,9 @@
       <c r="C11" s="3">
         <v>10</v>
       </c>
-      <c r="D11" s="12" t="e">
+      <c r="D11" s="12">
         <f>'Tong quan'!$B$3+(C11-1)</f>
-        <v>#VALUE!</v>
+        <v>46200</v>
       </c>
       <c r="E11" s="4" t="s">
         <v>111</v>
@@ -3581,7 +3582,7 @@
         <v>113</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="I11" s="3"/>
       <c r="J11" s="4"/>
@@ -3593,7 +3594,7 @@
         <v>91</v>
       </c>
       <c r="N11" s="3" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="O11" s="3"/>
     </row>
@@ -3607,9 +3608,9 @@
       <c r="C12" s="3">
         <v>11</v>
       </c>
-      <c r="D12" s="12" t="e">
+      <c r="D12" s="12">
         <f>'Tong quan'!$B$3+(C12-1)</f>
-        <v>#VALUE!</v>
+        <v>46201</v>
       </c>
       <c r="E12" s="4" t="s">
         <v>115</v>
@@ -3621,7 +3622,7 @@
         <v>117</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="I12" s="3"/>
       <c r="J12" s="4"/>
@@ -3633,7 +3634,7 @@
         <v>91</v>
       </c>
       <c r="N12" s="3" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="O12" s="3"/>
     </row>
@@ -3647,9 +3648,9 @@
       <c r="C13" s="3">
         <v>12</v>
       </c>
-      <c r="D13" s="12" t="e">
+      <c r="D13" s="12">
         <f>'Tong quan'!$B$3+(C13-1)</f>
-        <v>#VALUE!</v>
+        <v>46202</v>
       </c>
       <c r="E13" s="4" t="s">
         <v>119</v>
@@ -3661,7 +3662,7 @@
         <v>121</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="I13" s="3"/>
       <c r="J13" s="4"/>
@@ -3670,10 +3671,10 @@
         <v>122</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="N13" s="3" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="O13" s="3"/>
     </row>
@@ -3687,9 +3688,9 @@
       <c r="C14" s="3">
         <v>13</v>
       </c>
-      <c r="D14" s="12" t="e">
+      <c r="D14" s="12">
         <f>'Tong quan'!$B$3+(C14-1)</f>
-        <v>#VALUE!</v>
+        <v>46203</v>
       </c>
       <c r="E14" s="4" t="s">
         <v>123</v>
@@ -3701,7 +3702,7 @@
         <v>124</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="I14" s="3"/>
       <c r="J14" s="4"/>
@@ -3713,7 +3714,7 @@
         <v>91</v>
       </c>
       <c r="N14" s="3" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="O14" s="3"/>
     </row>
@@ -3727,9 +3728,9 @@
       <c r="C15" s="13">
         <v>14</v>
       </c>
-      <c r="D15" s="14" t="e">
+      <c r="D15" s="14">
         <f>'Tong quan'!$B$3+(C15-1)</f>
-        <v>#VALUE!</v>
+        <v>46204</v>
       </c>
       <c r="E15" s="15" t="s">
         <v>126</v>
@@ -3741,7 +3742,7 @@
         <v>127</v>
       </c>
       <c r="H15" s="13" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="I15" s="13"/>
       <c r="J15" s="15"/>
@@ -3753,7 +3754,7 @@
         <v>91</v>
       </c>
       <c r="N15" s="13" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="O15" s="13"/>
     </row>
@@ -3767,9 +3768,9 @@
       <c r="C16" s="3">
         <v>15</v>
       </c>
-      <c r="D16" s="12" t="e">
+      <c r="D16" s="12">
         <f>'Tong quan'!$B$3+(C16-1)</f>
-        <v>#VALUE!</v>
+        <v>46205</v>
       </c>
       <c r="E16" s="4" t="s">
         <v>129</v>
@@ -3781,21 +3782,21 @@
         <v>131</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="I16" s="3"/>
       <c r="J16" s="4"/>
       <c r="K16" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L16" s="3" t="s">
         <v>132</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="N16" s="3" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="O16" s="3"/>
     </row>
@@ -3809,9 +3810,9 @@
       <c r="C17" s="3">
         <v>16</v>
       </c>
-      <c r="D17" s="12" t="e">
+      <c r="D17" s="12">
         <f>'Tong quan'!$B$3+(C17-1)</f>
-        <v>#VALUE!</v>
+        <v>46206</v>
       </c>
       <c r="E17" s="4" t="s">
         <v>133</v>
@@ -3823,7 +3824,7 @@
         <v>135</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="I17" s="3"/>
       <c r="J17" s="4"/>
@@ -3835,7 +3836,7 @@
         <v>91</v>
       </c>
       <c r="N17" s="3" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="O17" s="3"/>
     </row>
@@ -3849,9 +3850,9 @@
       <c r="C18" s="3">
         <v>17</v>
       </c>
-      <c r="D18" s="12" t="e">
+      <c r="D18" s="12">
         <f>'Tong quan'!$B$3+(C18-1)</f>
-        <v>#VALUE!</v>
+        <v>46207</v>
       </c>
       <c r="E18" s="4" t="s">
         <v>137</v>
@@ -3863,7 +3864,7 @@
         <v>139</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="I18" s="3"/>
       <c r="J18" s="4"/>
@@ -3875,7 +3876,7 @@
         <v>91</v>
       </c>
       <c r="N18" s="3" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="O18" s="3"/>
     </row>
@@ -3889,9 +3890,9 @@
       <c r="C19" s="3">
         <v>18</v>
       </c>
-      <c r="D19" s="12" t="e">
+      <c r="D19" s="12">
         <f>'Tong quan'!$B$3+(C19-1)</f>
-        <v>#VALUE!</v>
+        <v>46208</v>
       </c>
       <c r="E19" s="4" t="s">
         <v>141</v>
@@ -3903,7 +3904,7 @@
         <v>143</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="I19" s="3"/>
       <c r="J19" s="4"/>
@@ -3915,7 +3916,7 @@
         <v>91</v>
       </c>
       <c r="N19" s="3" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="O19" s="3"/>
     </row>
@@ -3929,9 +3930,9 @@
       <c r="C20" s="3">
         <v>19</v>
       </c>
-      <c r="D20" s="12" t="e">
+      <c r="D20" s="12">
         <f>'Tong quan'!$B$3+(C20-1)</f>
-        <v>#VALUE!</v>
+        <v>46209</v>
       </c>
       <c r="E20" s="4" t="s">
         <v>145</v>
@@ -3943,7 +3944,7 @@
         <v>147</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="I20" s="3"/>
       <c r="J20" s="4"/>
@@ -3955,7 +3956,7 @@
         <v>91</v>
       </c>
       <c r="N20" s="3" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="O20" s="3"/>
     </row>
@@ -3969,9 +3970,9 @@
       <c r="C21" s="3">
         <v>20</v>
       </c>
-      <c r="D21" s="12" t="e">
+      <c r="D21" s="12">
         <f>'Tong quan'!$B$3+(C21-1)</f>
-        <v>#VALUE!</v>
+        <v>46210</v>
       </c>
       <c r="E21" s="4" t="s">
         <v>149</v>
@@ -3983,7 +3984,7 @@
         <v>150</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="I21" s="3"/>
       <c r="J21" s="4"/>
@@ -3995,7 +3996,7 @@
         <v>91</v>
       </c>
       <c r="N21" s="3" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="O21" s="3"/>
     </row>
@@ -4009,9 +4010,9 @@
       <c r="C22" s="13">
         <v>21</v>
       </c>
-      <c r="D22" s="14" t="e">
+      <c r="D22" s="14">
         <f>'Tong quan'!$B$3+(C22-1)</f>
-        <v>#VALUE!</v>
+        <v>46211</v>
       </c>
       <c r="E22" s="15" t="s">
         <v>152</v>
@@ -4023,7 +4024,7 @@
         <v>153</v>
       </c>
       <c r="H22" s="13" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="I22" s="13"/>
       <c r="J22" s="15"/>
@@ -4035,7 +4036,7 @@
         <v>155</v>
       </c>
       <c r="N22" s="13" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="O22" s="13"/>
     </row>
@@ -4049,9 +4050,9 @@
       <c r="C23" s="3">
         <v>22</v>
       </c>
-      <c r="D23" s="12" t="e">
+      <c r="D23" s="12">
         <f>'Tong quan'!$B$3+(C23-1)</f>
-        <v>#VALUE!</v>
+        <v>46212</v>
       </c>
       <c r="E23" s="4" t="s">
         <v>156</v>
@@ -4063,21 +4064,21 @@
         <v>157</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="I23" s="3"/>
       <c r="J23" s="4"/>
       <c r="K23" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L23" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M23" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="N23" s="3" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="O23" s="3"/>
     </row>
@@ -4091,9 +4092,9 @@
       <c r="C24" s="3">
         <v>23</v>
       </c>
-      <c r="D24" s="12" t="e">
+      <c r="D24" s="12">
         <f>'Tong quan'!$B$3+(C24-1)</f>
-        <v>#VALUE!</v>
+        <v>46213</v>
       </c>
       <c r="E24" s="4" t="s">
         <v>158</v>
@@ -4105,7 +4106,7 @@
         <v>160</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="I24" s="3"/>
       <c r="J24" s="4"/>
@@ -4117,7 +4118,7 @@
         <v>91</v>
       </c>
       <c r="N24" s="3" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="O24" s="3"/>
     </row>
@@ -4131,9 +4132,9 @@
       <c r="C25" s="3">
         <v>24</v>
       </c>
-      <c r="D25" s="12" t="e">
+      <c r="D25" s="12">
         <f>'Tong quan'!$B$3+(C25-1)</f>
-        <v>#VALUE!</v>
+        <v>46214</v>
       </c>
       <c r="E25" s="4" t="s">
         <v>162</v>
@@ -4145,7 +4146,7 @@
         <v>164</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="I25" s="3"/>
       <c r="J25" s="4"/>
@@ -4157,7 +4158,7 @@
         <v>91</v>
       </c>
       <c r="N25" s="3" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="O25" s="3"/>
     </row>
@@ -4171,9 +4172,9 @@
       <c r="C26" s="3">
         <v>25</v>
       </c>
-      <c r="D26" s="12" t="e">
+      <c r="D26" s="12">
         <f>'Tong quan'!$B$3+(C26-1)</f>
-        <v>#VALUE!</v>
+        <v>46215</v>
       </c>
       <c r="E26" s="4" t="s">
         <v>166</v>
@@ -4185,7 +4186,7 @@
         <v>168</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="I26" s="3"/>
       <c r="J26" s="4"/>
@@ -4197,7 +4198,7 @@
         <v>91</v>
       </c>
       <c r="N26" s="3" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="O26" s="3"/>
     </row>
@@ -4211,9 +4212,9 @@
       <c r="C27" s="3">
         <v>26</v>
       </c>
-      <c r="D27" s="12" t="e">
+      <c r="D27" s="12">
         <f>'Tong quan'!$B$3+(C27-1)</f>
-        <v>#VALUE!</v>
+        <v>46216</v>
       </c>
       <c r="E27" s="4" t="s">
         <v>170</v>
@@ -4225,7 +4226,7 @@
         <v>172</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="I27" s="3"/>
       <c r="J27" s="4"/>
@@ -4237,7 +4238,7 @@
         <v>91</v>
       </c>
       <c r="N27" s="3" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="O27" s="3"/>
     </row>
@@ -4251,9 +4252,9 @@
       <c r="C28" s="3">
         <v>27</v>
       </c>
-      <c r="D28" s="12" t="e">
+      <c r="D28" s="12">
         <f>'Tong quan'!$B$3+(C28-1)</f>
-        <v>#VALUE!</v>
+        <v>46217</v>
       </c>
       <c r="E28" s="4" t="s">
         <v>174</v>
@@ -4265,7 +4266,7 @@
         <v>175</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="I28" s="3"/>
       <c r="J28" s="4"/>
@@ -4277,7 +4278,7 @@
         <v>91</v>
       </c>
       <c r="N28" s="3" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="O28" s="3"/>
     </row>
@@ -4291,9 +4292,9 @@
       <c r="C29" s="13">
         <v>28</v>
       </c>
-      <c r="D29" s="14" t="e">
+      <c r="D29" s="14">
         <f>'Tong quan'!$B$3+(C29-1)</f>
-        <v>#VALUE!</v>
+        <v>46218</v>
       </c>
       <c r="E29" s="15" t="s">
         <v>177</v>
@@ -4305,7 +4306,7 @@
         <v>178</v>
       </c>
       <c r="H29" s="13" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="I29" s="13"/>
       <c r="J29" s="15"/>
@@ -4317,7 +4318,7 @@
         <v>155</v>
       </c>
       <c r="N29" s="13" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="O29" s="13"/>
     </row>
@@ -4331,9 +4332,9 @@
       <c r="C30" s="3">
         <v>29</v>
       </c>
-      <c r="D30" s="12" t="e">
+      <c r="D30" s="12">
         <f>'Tong quan'!$B$3+(C30-1)</f>
-        <v>#VALUE!</v>
+        <v>46219</v>
       </c>
       <c r="E30" s="4" t="s">
         <v>180</v>
@@ -4345,21 +4346,21 @@
         <v>182</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="I30" s="3"/>
       <c r="J30" s="4"/>
       <c r="K30" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="L30" s="3" t="s">
         <v>183</v>
       </c>
       <c r="M30" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="N30" s="3" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="O30" s="3"/>
     </row>
@@ -4373,9 +4374,9 @@
       <c r="C31" s="3">
         <v>30</v>
       </c>
-      <c r="D31" s="12" t="e">
+      <c r="D31" s="12">
         <f>'Tong quan'!$B$3+(C31-1)</f>
-        <v>#VALUE!</v>
+        <v>46220</v>
       </c>
       <c r="E31" s="4" t="s">
         <v>184</v>
@@ -4387,7 +4388,7 @@
         <v>186</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="I31" s="3"/>
       <c r="J31" s="4"/>
@@ -4396,10 +4397,10 @@
         <v>187</v>
       </c>
       <c r="M31" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="N31" s="3" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="O31" s="3"/>
     </row>
@@ -4413,9 +4414,9 @@
       <c r="C32" s="3">
         <v>31</v>
       </c>
-      <c r="D32" s="12" t="e">
+      <c r="D32" s="12">
         <f>'Tong quan'!$B$3+(C32-1)</f>
-        <v>#VALUE!</v>
+        <v>46221</v>
       </c>
       <c r="E32" s="4" t="s">
         <v>188</v>
@@ -4427,7 +4428,7 @@
         <v>190</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="I32" s="3"/>
       <c r="J32" s="4"/>
@@ -4439,7 +4440,7 @@
         <v>91</v>
       </c>
       <c r="N32" s="3" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="O32" s="3"/>
     </row>
@@ -4453,9 +4454,9 @@
       <c r="C33" s="3">
         <v>32</v>
       </c>
-      <c r="D33" s="12" t="e">
+      <c r="D33" s="12">
         <f>'Tong quan'!$B$3+(C33-1)</f>
-        <v>#VALUE!</v>
+        <v>46222</v>
       </c>
       <c r="E33" s="4" t="s">
         <v>192</v>
@@ -4467,7 +4468,7 @@
         <v>194</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="I33" s="3"/>
       <c r="J33" s="4"/>
@@ -4479,7 +4480,7 @@
         <v>91</v>
       </c>
       <c r="N33" s="3" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="O33" s="3"/>
     </row>
@@ -4493,9 +4494,9 @@
       <c r="C34" s="3">
         <v>33</v>
       </c>
-      <c r="D34" s="12" t="e">
+      <c r="D34" s="12">
         <f>'Tong quan'!$B$3+(C34-1)</f>
-        <v>#VALUE!</v>
+        <v>46223</v>
       </c>
       <c r="E34" s="4" t="s">
         <v>196</v>
@@ -4507,7 +4508,7 @@
         <v>198</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="I34" s="3"/>
       <c r="J34" s="4"/>
@@ -4519,7 +4520,7 @@
         <v>91</v>
       </c>
       <c r="N34" s="3" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="O34" s="3"/>
     </row>
@@ -4533,9 +4534,9 @@
       <c r="C35" s="3">
         <v>34</v>
       </c>
-      <c r="D35" s="12" t="e">
+      <c r="D35" s="12">
         <f>'Tong quan'!$B$3+(C35-1)</f>
-        <v>#VALUE!</v>
+        <v>46224</v>
       </c>
       <c r="E35" s="4" t="s">
         <v>200</v>
@@ -4547,7 +4548,7 @@
         <v>201</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="I35" s="3"/>
       <c r="J35" s="4"/>
@@ -4559,7 +4560,7 @@
         <v>91</v>
       </c>
       <c r="N35" s="3" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="O35" s="3"/>
     </row>
@@ -4573,9 +4574,9 @@
       <c r="C36" s="13">
         <v>35</v>
       </c>
-      <c r="D36" s="14" t="e">
+      <c r="D36" s="14">
         <f>'Tong quan'!$B$3+(C36-1)</f>
-        <v>#VALUE!</v>
+        <v>46225</v>
       </c>
       <c r="E36" s="15" t="s">
         <v>203</v>
@@ -4587,7 +4588,7 @@
         <v>204</v>
       </c>
       <c r="H36" s="13" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="I36" s="13"/>
       <c r="J36" s="15"/>
@@ -4596,10 +4597,10 @@
         <v>205</v>
       </c>
       <c r="M36" s="13" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="N36" s="13" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="O36" s="13"/>
     </row>
@@ -4613,9 +4614,9 @@
       <c r="C37" s="3">
         <v>36</v>
       </c>
-      <c r="D37" s="12" t="e">
+      <c r="D37" s="12">
         <f>'Tong quan'!$B$3+(C37-1)</f>
-        <v>#VALUE!</v>
+        <v>46226</v>
       </c>
       <c r="E37" s="4" t="s">
         <v>206</v>
@@ -4627,21 +4628,21 @@
         <v>208</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="I37" s="3"/>
       <c r="J37" s="4"/>
       <c r="K37" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L37" s="3" t="s">
         <v>209</v>
       </c>
       <c r="M37" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="N37" s="3" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="O37" s="3"/>
     </row>
@@ -4655,9 +4656,9 @@
       <c r="C38" s="3">
         <v>37</v>
       </c>
-      <c r="D38" s="12" t="e">
+      <c r="D38" s="12">
         <f>'Tong quan'!$B$3+(C38-1)</f>
-        <v>#VALUE!</v>
+        <v>46227</v>
       </c>
       <c r="E38" s="4" t="s">
         <v>210</v>
@@ -4669,7 +4670,7 @@
         <v>211</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="I38" s="3"/>
       <c r="J38" s="4"/>
@@ -4678,10 +4679,10 @@
         <v>212</v>
       </c>
       <c r="M38" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="N38" s="3" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="O38" s="3"/>
     </row>
@@ -4695,9 +4696,9 @@
       <c r="C39" s="3">
         <v>38</v>
       </c>
-      <c r="D39" s="12" t="e">
+      <c r="D39" s="12">
         <f>'Tong quan'!$B$3+(C39-1)</f>
-        <v>#VALUE!</v>
+        <v>46228</v>
       </c>
       <c r="E39" s="4" t="s">
         <v>213</v>
@@ -4709,7 +4710,7 @@
         <v>215</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="I39" s="3"/>
       <c r="J39" s="4"/>
@@ -4718,10 +4719,10 @@
         <v>216</v>
       </c>
       <c r="M39" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="N39" s="3" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="O39" s="3"/>
     </row>
@@ -4735,9 +4736,9 @@
       <c r="C40" s="3">
         <v>39</v>
       </c>
-      <c r="D40" s="12" t="e">
+      <c r="D40" s="12">
         <f>'Tong quan'!$B$3+(C40-1)</f>
-        <v>#VALUE!</v>
+        <v>46229</v>
       </c>
       <c r="E40" s="4" t="s">
         <v>217</v>
@@ -4749,7 +4750,7 @@
         <v>219</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="I40" s="3"/>
       <c r="J40" s="4"/>
@@ -4758,10 +4759,10 @@
         <v>220</v>
       </c>
       <c r="M40" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="N40" s="3" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="O40" s="3"/>
     </row>
@@ -4775,9 +4776,9 @@
       <c r="C41" s="3">
         <v>40</v>
       </c>
-      <c r="D41" s="12" t="e">
+      <c r="D41" s="12">
         <f>'Tong quan'!$B$3+(C41-1)</f>
-        <v>#VALUE!</v>
+        <v>46230</v>
       </c>
       <c r="E41" s="4" t="s">
         <v>221</v>
@@ -4789,7 +4790,7 @@
         <v>223</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="I41" s="3"/>
       <c r="J41" s="4"/>
@@ -4801,7 +4802,7 @@
         <v>91</v>
       </c>
       <c r="N41" s="3" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="O41" s="3"/>
     </row>
@@ -4815,9 +4816,9 @@
       <c r="C42" s="3">
         <v>41</v>
       </c>
-      <c r="D42" s="12" t="e">
+      <c r="D42" s="12">
         <f>'Tong quan'!$B$3+(C42-1)</f>
-        <v>#VALUE!</v>
+        <v>46231</v>
       </c>
       <c r="E42" s="4" t="s">
         <v>225</v>
@@ -4829,7 +4830,7 @@
         <v>226</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="I42" s="3"/>
       <c r="J42" s="4"/>
@@ -4841,7 +4842,7 @@
         <v>91</v>
       </c>
       <c r="N42" s="3" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="O42" s="3"/>
     </row>
@@ -4855,9 +4856,9 @@
       <c r="C43" s="13">
         <v>42</v>
       </c>
-      <c r="D43" s="14" t="e">
+      <c r="D43" s="14">
         <f>'Tong quan'!$B$3+(C43-1)</f>
-        <v>#VALUE!</v>
+        <v>46232</v>
       </c>
       <c r="E43" s="15" t="s">
         <v>228</v>
@@ -4869,7 +4870,7 @@
         <v>229</v>
       </c>
       <c r="H43" s="13" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="I43" s="13"/>
       <c r="J43" s="15"/>
@@ -4881,7 +4882,7 @@
         <v>91</v>
       </c>
       <c r="N43" s="13" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="O43" s="13"/>
     </row>
@@ -4895,9 +4896,9 @@
       <c r="C44" s="3">
         <v>43</v>
       </c>
-      <c r="D44" s="12" t="e">
+      <c r="D44" s="12">
         <f>'Tong quan'!$B$3+(C44-1)</f>
-        <v>#VALUE!</v>
+        <v>46233</v>
       </c>
       <c r="E44" s="4" t="s">
         <v>231</v>
@@ -4909,12 +4910,12 @@
         <v>233</v>
       </c>
       <c r="H44" s="3" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="I44" s="3"/>
       <c r="J44" s="4"/>
       <c r="K44" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="L44" s="3" t="s">
         <v>234</v>
@@ -4923,7 +4924,7 @@
         <v>91</v>
       </c>
       <c r="N44" s="3" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="O44" s="3"/>
     </row>
@@ -4937,9 +4938,9 @@
       <c r="C45" s="3">
         <v>44</v>
       </c>
-      <c r="D45" s="12" t="e">
+      <c r="D45" s="12">
         <f>'Tong quan'!$B$3+(C45-1)</f>
-        <v>#VALUE!</v>
+        <v>46234</v>
       </c>
       <c r="E45" s="4" t="s">
         <v>235</v>
@@ -4951,7 +4952,7 @@
         <v>237</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="I45" s="3"/>
       <c r="J45" s="4"/>
@@ -4963,7 +4964,7 @@
         <v>91</v>
       </c>
       <c r="N45" s="3" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="O45" s="3"/>
     </row>
@@ -4977,9 +4978,9 @@
       <c r="C46" s="3">
         <v>45</v>
       </c>
-      <c r="D46" s="12" t="e">
+      <c r="D46" s="12">
         <f>'Tong quan'!$B$3+(C46-1)</f>
-        <v>#VALUE!</v>
+        <v>46235</v>
       </c>
       <c r="E46" s="4" t="s">
         <v>239</v>
@@ -4991,7 +4992,7 @@
         <v>241</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="I46" s="3"/>
       <c r="J46" s="4"/>
@@ -5003,7 +5004,7 @@
         <v>91</v>
       </c>
       <c r="N46" s="3" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="O46" s="3"/>
     </row>
@@ -5017,9 +5018,9 @@
       <c r="C47" s="3">
         <v>46</v>
       </c>
-      <c r="D47" s="12" t="e">
+      <c r="D47" s="12">
         <f>'Tong quan'!$B$3+(C47-1)</f>
-        <v>#VALUE!</v>
+        <v>46236</v>
       </c>
       <c r="E47" s="4" t="s">
         <v>243</v>
@@ -5031,7 +5032,7 @@
         <v>245</v>
       </c>
       <c r="H47" s="3" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="I47" s="3"/>
       <c r="J47" s="4"/>
@@ -5043,7 +5044,7 @@
         <v>91</v>
       </c>
       <c r="N47" s="3" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="O47" s="3"/>
     </row>
@@ -5057,9 +5058,9 @@
       <c r="C48" s="3">
         <v>47</v>
       </c>
-      <c r="D48" s="12" t="e">
+      <c r="D48" s="12">
         <f>'Tong quan'!$B$3+(C48-1)</f>
-        <v>#VALUE!</v>
+        <v>46237</v>
       </c>
       <c r="E48" s="4" t="s">
         <v>247</v>
@@ -5071,7 +5072,7 @@
         <v>249</v>
       </c>
       <c r="H48" s="3" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="I48" s="3"/>
       <c r="J48" s="4"/>
@@ -5080,10 +5081,10 @@
         <v>250</v>
       </c>
       <c r="M48" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="N48" s="3" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="O48" s="3"/>
     </row>
@@ -5097,9 +5098,9 @@
       <c r="C49" s="3">
         <v>48</v>
       </c>
-      <c r="D49" s="12" t="e">
+      <c r="D49" s="12">
         <f>'Tong quan'!$B$3+(C49-1)</f>
-        <v>#VALUE!</v>
+        <v>46238</v>
       </c>
       <c r="E49" s="4" t="s">
         <v>251</v>
@@ -5111,7 +5112,7 @@
         <v>252</v>
       </c>
       <c r="H49" s="3" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="I49" s="3"/>
       <c r="J49" s="4"/>
@@ -5123,7 +5124,7 @@
         <v>91</v>
       </c>
       <c r="N49" s="3" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="O49" s="3"/>
     </row>
@@ -5137,9 +5138,9 @@
       <c r="C50" s="13">
         <v>49</v>
       </c>
-      <c r="D50" s="14" t="e">
+      <c r="D50" s="14">
         <f>'Tong quan'!$B$3+(C50-1)</f>
-        <v>#VALUE!</v>
+        <v>46239</v>
       </c>
       <c r="E50" s="15" t="s">
         <v>254</v>
@@ -5151,7 +5152,7 @@
         <v>255</v>
       </c>
       <c r="H50" s="13" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="I50" s="13"/>
       <c r="J50" s="15"/>
@@ -5163,7 +5164,7 @@
         <v>91</v>
       </c>
       <c r="N50" s="13" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="O50" s="13"/>
     </row>
@@ -5177,9 +5178,9 @@
       <c r="C51" s="3">
         <v>50</v>
       </c>
-      <c r="D51" s="12" t="e">
+      <c r="D51" s="12">
         <f>'Tong quan'!$B$3+(C51-1)</f>
-        <v>#VALUE!</v>
+        <v>46240</v>
       </c>
       <c r="E51" s="4" t="s">
         <v>257</v>
@@ -5191,12 +5192,12 @@
         <v>259</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="I51" s="3"/>
       <c r="J51" s="4"/>
       <c r="K51" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="L51" s="3" t="s">
         <v>260</v>
@@ -5205,7 +5206,7 @@
         <v>91</v>
       </c>
       <c r="N51" s="3" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="O51" s="3"/>
     </row>
@@ -5219,9 +5220,9 @@
       <c r="C52" s="3">
         <v>51</v>
       </c>
-      <c r="D52" s="12" t="e">
+      <c r="D52" s="12">
         <f>'Tong quan'!$B$3+(C52-1)</f>
-        <v>#VALUE!</v>
+        <v>46241</v>
       </c>
       <c r="E52" s="4" t="s">
         <v>261</v>
@@ -5233,7 +5234,7 @@
         <v>263</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="I52" s="3"/>
       <c r="J52" s="4"/>
@@ -5245,7 +5246,7 @@
         <v>91</v>
       </c>
       <c r="N52" s="3" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="O52" s="3"/>
     </row>
@@ -5259,9 +5260,9 @@
       <c r="C53" s="3">
         <v>52</v>
       </c>
-      <c r="D53" s="12" t="e">
+      <c r="D53" s="12">
         <f>'Tong quan'!$B$3+(C53-1)</f>
-        <v>#VALUE!</v>
+        <v>46242</v>
       </c>
       <c r="E53" s="4" t="s">
         <v>265</v>
@@ -5273,7 +5274,7 @@
         <v>266</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="I53" s="3"/>
       <c r="J53" s="4"/>
@@ -5285,7 +5286,7 @@
         <v>91</v>
       </c>
       <c r="N53" s="3" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="O53" s="3"/>
     </row>
@@ -5299,9 +5300,9 @@
       <c r="C54" s="3">
         <v>53</v>
       </c>
-      <c r="D54" s="12" t="e">
+      <c r="D54" s="12">
         <f>'Tong quan'!$B$3+(C54-1)</f>
-        <v>#VALUE!</v>
+        <v>46243</v>
       </c>
       <c r="E54" s="4" t="s">
         <v>268</v>
@@ -5313,7 +5314,7 @@
         <v>269</v>
       </c>
       <c r="H54" s="3" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="I54" s="3"/>
       <c r="J54" s="4"/>
@@ -5325,7 +5326,7 @@
         <v>91</v>
       </c>
       <c r="N54" s="3" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="O54" s="3"/>
     </row>
@@ -5339,9 +5340,9 @@
       <c r="C55" s="3">
         <v>54</v>
       </c>
-      <c r="D55" s="12" t="e">
+      <c r="D55" s="12">
         <f>'Tong quan'!$B$3+(C55-1)</f>
-        <v>#VALUE!</v>
+        <v>46244</v>
       </c>
       <c r="E55" s="4" t="s">
         <v>271</v>
@@ -5353,7 +5354,7 @@
         <v>272</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="I55" s="3"/>
       <c r="J55" s="4"/>
@@ -5365,7 +5366,7 @@
         <v>91</v>
       </c>
       <c r="N55" s="3" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="O55" s="3"/>
     </row>
@@ -5379,9 +5380,9 @@
       <c r="C56" s="3">
         <v>55</v>
       </c>
-      <c r="D56" s="12" t="e">
+      <c r="D56" s="12">
         <f>'Tong quan'!$B$3+(C56-1)</f>
-        <v>#VALUE!</v>
+        <v>46245</v>
       </c>
       <c r="E56" s="4" t="s">
         <v>274</v>
@@ -5393,7 +5394,7 @@
         <v>276</v>
       </c>
       <c r="H56" s="3" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="I56" s="3"/>
       <c r="J56" s="4"/>
@@ -5405,7 +5406,7 @@
         <v>91</v>
       </c>
       <c r="N56" s="3" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="O56" s="3"/>
     </row>
@@ -5419,9 +5420,9 @@
       <c r="C57" s="13">
         <v>56</v>
       </c>
-      <c r="D57" s="14" t="e">
+      <c r="D57" s="14">
         <f>'Tong quan'!$B$3+(C57-1)</f>
-        <v>#VALUE!</v>
+        <v>46246</v>
       </c>
       <c r="E57" s="15" t="s">
         <v>278</v>
@@ -5433,7 +5434,7 @@
         <v>279</v>
       </c>
       <c r="H57" s="13" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="I57" s="13"/>
       <c r="J57" s="15"/>
@@ -5445,7 +5446,7 @@
         <v>155</v>
       </c>
       <c r="N57" s="13" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="O57" s="13"/>
     </row>
@@ -5459,9 +5460,9 @@
       <c r="C58" s="3">
         <v>57</v>
       </c>
-      <c r="D58" s="12" t="e">
+      <c r="D58" s="12">
         <f>'Tong quan'!$B$3+(C58-1)</f>
-        <v>#VALUE!</v>
+        <v>46247</v>
       </c>
       <c r="E58" s="4" t="s">
         <v>281</v>
@@ -5473,12 +5474,12 @@
         <v>283</v>
       </c>
       <c r="H58" s="3" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="I58" s="3"/>
       <c r="J58" s="4"/>
       <c r="K58" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="L58" s="3" t="s">
         <v>284</v>
@@ -5487,7 +5488,7 @@
         <v>91</v>
       </c>
       <c r="N58" s="3" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="O58" s="3"/>
     </row>
@@ -5501,9 +5502,9 @@
       <c r="C59" s="3">
         <v>58</v>
       </c>
-      <c r="D59" s="12" t="e">
+      <c r="D59" s="12">
         <f>'Tong quan'!$B$3+(C59-1)</f>
-        <v>#VALUE!</v>
+        <v>46248</v>
       </c>
       <c r="E59" s="4" t="s">
         <v>285</v>
@@ -5515,7 +5516,7 @@
         <v>287</v>
       </c>
       <c r="H59" s="3" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="I59" s="3"/>
       <c r="J59" s="4"/>
@@ -5527,7 +5528,7 @@
         <v>91</v>
       </c>
       <c r="N59" s="3" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="O59" s="3"/>
     </row>
@@ -5541,9 +5542,9 @@
       <c r="C60" s="3">
         <v>59</v>
       </c>
-      <c r="D60" s="12" t="e">
+      <c r="D60" s="12">
         <f>'Tong quan'!$B$3+(C60-1)</f>
-        <v>#VALUE!</v>
+        <v>46249</v>
       </c>
       <c r="E60" s="4" t="s">
         <v>289</v>
@@ -5555,7 +5556,7 @@
         <v>291</v>
       </c>
       <c r="H60" s="3" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="I60" s="3"/>
       <c r="J60" s="4"/>
@@ -5567,7 +5568,7 @@
         <v>91</v>
       </c>
       <c r="N60" s="3" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="O60" s="3"/>
     </row>
@@ -5581,9 +5582,9 @@
       <c r="C61" s="3">
         <v>60</v>
       </c>
-      <c r="D61" s="12" t="e">
+      <c r="D61" s="12">
         <f>'Tong quan'!$B$3+(C61-1)</f>
-        <v>#VALUE!</v>
+        <v>46250</v>
       </c>
       <c r="E61" s="4" t="s">
         <v>293</v>
@@ -5595,7 +5596,7 @@
         <v>295</v>
       </c>
       <c r="H61" s="3" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="I61" s="3"/>
       <c r="J61" s="4"/>
@@ -5607,7 +5608,7 @@
         <v>91</v>
       </c>
       <c r="N61" s="3" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="O61" s="3"/>
     </row>
@@ -5621,9 +5622,9 @@
       <c r="C62" s="3">
         <v>61</v>
       </c>
-      <c r="D62" s="12" t="e">
+      <c r="D62" s="12">
         <f>'Tong quan'!$B$3+(C62-1)</f>
-        <v>#VALUE!</v>
+        <v>46251</v>
       </c>
       <c r="E62" s="4" t="s">
         <v>297</v>
@@ -5635,7 +5636,7 @@
         <v>298</v>
       </c>
       <c r="H62" s="3" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="I62" s="3"/>
       <c r="J62" s="4"/>
@@ -5647,7 +5648,7 @@
         <v>91</v>
       </c>
       <c r="N62" s="3" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="O62" s="3"/>
     </row>
@@ -5661,9 +5662,9 @@
       <c r="C63" s="3">
         <v>62</v>
       </c>
-      <c r="D63" s="12" t="e">
+      <c r="D63" s="12">
         <f>'Tong quan'!$B$3+(C63-1)</f>
-        <v>#VALUE!</v>
+        <v>46252</v>
       </c>
       <c r="E63" s="4" t="s">
         <v>300</v>
@@ -5675,7 +5676,7 @@
         <v>301</v>
       </c>
       <c r="H63" s="3" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="I63" s="3"/>
       <c r="J63" s="4"/>
@@ -5687,7 +5688,7 @@
         <v>91</v>
       </c>
       <c r="N63" s="3" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="O63" s="3"/>
     </row>
@@ -5701,9 +5702,9 @@
       <c r="C64" s="13">
         <v>63</v>
       </c>
-      <c r="D64" s="14" t="e">
+      <c r="D64" s="14">
         <f>'Tong quan'!$B$3+(C64-1)</f>
-        <v>#VALUE!</v>
+        <v>46253</v>
       </c>
       <c r="E64" s="15" t="s">
         <v>303</v>
@@ -5715,7 +5716,7 @@
         <v>304</v>
       </c>
       <c r="H64" s="13" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="I64" s="13"/>
       <c r="J64" s="15"/>
@@ -5727,7 +5728,7 @@
         <v>91</v>
       </c>
       <c r="N64" s="13" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="O64" s="13"/>
     </row>
@@ -5741,9 +5742,9 @@
       <c r="C65" s="3">
         <v>64</v>
       </c>
-      <c r="D65" s="12" t="e">
+      <c r="D65" s="12">
         <f>'Tong quan'!$B$3+(C65-1)</f>
-        <v>#VALUE!</v>
+        <v>46254</v>
       </c>
       <c r="E65" s="4" t="s">
         <v>306</v>
@@ -5755,12 +5756,12 @@
         <v>308</v>
       </c>
       <c r="H65" s="3" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="I65" s="3"/>
       <c r="J65" s="4"/>
       <c r="K65" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="L65" s="3" t="s">
         <v>309</v>
@@ -5769,7 +5770,7 @@
         <v>91</v>
       </c>
       <c r="N65" s="3" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="O65" s="3"/>
     </row>
@@ -5783,9 +5784,9 @@
       <c r="C66" s="3">
         <v>65</v>
       </c>
-      <c r="D66" s="12" t="e">
+      <c r="D66" s="12">
         <f>'Tong quan'!$B$3+(C66-1)</f>
-        <v>#VALUE!</v>
+        <v>46255</v>
       </c>
       <c r="E66" s="4" t="s">
         <v>310</v>
@@ -5797,7 +5798,7 @@
         <v>312</v>
       </c>
       <c r="H66" s="3" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="I66" s="3"/>
       <c r="J66" s="4"/>
@@ -5809,7 +5810,7 @@
         <v>91</v>
       </c>
       <c r="N66" s="3" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="O66" s="3"/>
     </row>
@@ -5823,9 +5824,9 @@
       <c r="C67" s="3">
         <v>66</v>
       </c>
-      <c r="D67" s="12" t="e">
+      <c r="D67" s="12">
         <f>'Tong quan'!$B$3+(C67-1)</f>
-        <v>#VALUE!</v>
+        <v>46256</v>
       </c>
       <c r="E67" s="4" t="s">
         <v>314</v>
@@ -5837,7 +5838,7 @@
         <v>316</v>
       </c>
       <c r="H67" s="3" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="I67" s="3"/>
       <c r="J67" s="4"/>
@@ -5849,7 +5850,7 @@
         <v>91</v>
       </c>
       <c r="N67" s="3" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="O67" s="3"/>
     </row>
@@ -5863,9 +5864,9 @@
       <c r="C68" s="3">
         <v>67</v>
       </c>
-      <c r="D68" s="12" t="e">
+      <c r="D68" s="12">
         <f>'Tong quan'!$B$3+(C68-1)</f>
-        <v>#VALUE!</v>
+        <v>46257</v>
       </c>
       <c r="E68" s="4" t="s">
         <v>318</v>
@@ -5877,7 +5878,7 @@
         <v>320</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="I68" s="3"/>
       <c r="J68" s="4"/>
@@ -5889,7 +5890,7 @@
         <v>91</v>
       </c>
       <c r="N68" s="3" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="O68" s="3"/>
     </row>
@@ -5903,9 +5904,9 @@
       <c r="C69" s="3">
         <v>68</v>
       </c>
-      <c r="D69" s="12" t="e">
+      <c r="D69" s="12">
         <f>'Tong quan'!$B$3+(C69-1)</f>
-        <v>#VALUE!</v>
+        <v>46258</v>
       </c>
       <c r="E69" s="4" t="s">
         <v>322</v>
@@ -5917,7 +5918,7 @@
         <v>323</v>
       </c>
       <c r="H69" s="3" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="I69" s="3"/>
       <c r="J69" s="4"/>
@@ -5929,7 +5930,7 @@
         <v>155</v>
       </c>
       <c r="N69" s="3" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="O69" s="3"/>
     </row>
@@ -5943,9 +5944,9 @@
       <c r="C70" s="3">
         <v>69</v>
       </c>
-      <c r="D70" s="12" t="e">
+      <c r="D70" s="12">
         <f>'Tong quan'!$B$3+(C70-1)</f>
-        <v>#VALUE!</v>
+        <v>46259</v>
       </c>
       <c r="E70" s="4" t="s">
         <v>325</v>
@@ -5957,7 +5958,7 @@
         <v>326</v>
       </c>
       <c r="H70" s="3" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="I70" s="3"/>
       <c r="J70" s="4"/>
@@ -5969,7 +5970,7 @@
         <v>155</v>
       </c>
       <c r="N70" s="3" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="O70" s="3"/>
     </row>
@@ -5983,9 +5984,9 @@
       <c r="C71" s="13">
         <v>70</v>
       </c>
-      <c r="D71" s="14" t="e">
+      <c r="D71" s="14">
         <f>'Tong quan'!$B$3+(C71-1)</f>
-        <v>#VALUE!</v>
+        <v>46260</v>
       </c>
       <c r="E71" s="15" t="s">
         <v>328</v>
@@ -5997,7 +5998,7 @@
         <v>329</v>
       </c>
       <c r="H71" s="13" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="I71" s="13"/>
       <c r="J71" s="15"/>
@@ -6009,7 +6010,7 @@
         <v>91</v>
       </c>
       <c r="N71" s="13" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="O71" s="13"/>
     </row>
@@ -6023,9 +6024,9 @@
       <c r="C72" s="3">
         <v>71</v>
       </c>
-      <c r="D72" s="12" t="e">
+      <c r="D72" s="12">
         <f>'Tong quan'!$B$3+(C72-1)</f>
-        <v>#VALUE!</v>
+        <v>46261</v>
       </c>
       <c r="E72" s="4" t="s">
         <v>331</v>
@@ -6037,21 +6038,21 @@
         <v>333</v>
       </c>
       <c r="H72" s="3" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="I72" s="3"/>
       <c r="J72" s="4"/>
       <c r="K72" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="L72" s="3" t="s">
         <v>334</v>
       </c>
       <c r="M72" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="N72" s="3" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="O72" s="3"/>
     </row>
@@ -6065,9 +6066,9 @@
       <c r="C73" s="3">
         <v>72</v>
       </c>
-      <c r="D73" s="12" t="e">
+      <c r="D73" s="12">
         <f>'Tong quan'!$B$3+(C73-1)</f>
-        <v>#VALUE!</v>
+        <v>46262</v>
       </c>
       <c r="E73" s="4" t="s">
         <v>335</v>
@@ -6079,7 +6080,7 @@
         <v>337</v>
       </c>
       <c r="H73" s="3" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="I73" s="3"/>
       <c r="J73" s="4"/>
@@ -6091,7 +6092,7 @@
         <v>91</v>
       </c>
       <c r="N73" s="3" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="O73" s="3"/>
     </row>
@@ -6105,9 +6106,9 @@
       <c r="C74" s="3">
         <v>73</v>
       </c>
-      <c r="D74" s="12" t="e">
+      <c r="D74" s="12">
         <f>'Tong quan'!$B$3+(C74-1)</f>
-        <v>#VALUE!</v>
+        <v>46263</v>
       </c>
       <c r="E74" s="4" t="s">
         <v>339</v>
@@ -6119,7 +6120,7 @@
         <v>341</v>
       </c>
       <c r="H74" s="3" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="I74" s="3"/>
       <c r="J74" s="4"/>
@@ -6131,7 +6132,7 @@
         <v>91</v>
       </c>
       <c r="N74" s="3" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="O74" s="3"/>
     </row>
@@ -6145,9 +6146,9 @@
       <c r="C75" s="3">
         <v>74</v>
       </c>
-      <c r="D75" s="12" t="e">
+      <c r="D75" s="12">
         <f>'Tong quan'!$B$3+(C75-1)</f>
-        <v>#VALUE!</v>
+        <v>46264</v>
       </c>
       <c r="E75" s="4" t="s">
         <v>343</v>
@@ -6159,7 +6160,7 @@
         <v>344</v>
       </c>
       <c r="H75" s="3" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="I75" s="3"/>
       <c r="J75" s="4"/>
@@ -6171,7 +6172,7 @@
         <v>91</v>
       </c>
       <c r="N75" s="3" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="O75" s="3"/>
     </row>
@@ -6185,9 +6186,9 @@
       <c r="C76" s="3">
         <v>75</v>
       </c>
-      <c r="D76" s="12" t="e">
+      <c r="D76" s="12">
         <f>'Tong quan'!$B$3+(C76-1)</f>
-        <v>#VALUE!</v>
+        <v>46265</v>
       </c>
       <c r="E76" s="4" t="s">
         <v>346</v>
@@ -6199,7 +6200,7 @@
         <v>348</v>
       </c>
       <c r="H76" s="3" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="I76" s="3"/>
       <c r="J76" s="4"/>
@@ -6211,7 +6212,7 @@
         <v>91</v>
       </c>
       <c r="N76" s="3" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="O76" s="3"/>
     </row>
@@ -6225,9 +6226,9 @@
       <c r="C77" s="3">
         <v>76</v>
       </c>
-      <c r="D77" s="12" t="e">
+      <c r="D77" s="12">
         <f>'Tong quan'!$B$3+(C77-1)</f>
-        <v>#VALUE!</v>
+        <v>46266</v>
       </c>
       <c r="E77" s="4" t="s">
         <v>350</v>
@@ -6239,7 +6240,7 @@
         <v>351</v>
       </c>
       <c r="H77" s="3" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="I77" s="3"/>
       <c r="J77" s="4"/>
@@ -6251,7 +6252,7 @@
         <v>91</v>
       </c>
       <c r="N77" s="3" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="O77" s="3"/>
     </row>
@@ -6265,9 +6266,9 @@
       <c r="C78" s="13">
         <v>77</v>
       </c>
-      <c r="D78" s="14" t="e">
+      <c r="D78" s="14">
         <f>'Tong quan'!$B$3+(C78-1)</f>
-        <v>#VALUE!</v>
+        <v>46267</v>
       </c>
       <c r="E78" s="15" t="s">
         <v>353</v>
@@ -6279,7 +6280,7 @@
         <v>354</v>
       </c>
       <c r="H78" s="13" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="I78" s="13"/>
       <c r="J78" s="15"/>
@@ -6291,7 +6292,7 @@
         <v>91</v>
       </c>
       <c r="N78" s="13" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="O78" s="13"/>
     </row>
@@ -6305,9 +6306,9 @@
       <c r="C79" s="3">
         <v>78</v>
       </c>
-      <c r="D79" s="12" t="e">
+      <c r="D79" s="12">
         <f>'Tong quan'!$B$3+(C79-1)</f>
-        <v>#VALUE!</v>
+        <v>46268</v>
       </c>
       <c r="E79" s="4" t="s">
         <v>356</v>
@@ -6319,12 +6320,12 @@
         <v>357</v>
       </c>
       <c r="H79" s="3" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="I79" s="3"/>
       <c r="J79" s="4"/>
       <c r="K79" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="L79" s="3" t="s">
         <v>358</v>
@@ -6333,7 +6334,7 @@
         <v>91</v>
       </c>
       <c r="N79" s="3" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="O79" s="3"/>
     </row>
@@ -6347,9 +6348,9 @@
       <c r="C80" s="3">
         <v>79</v>
       </c>
-      <c r="D80" s="12" t="e">
+      <c r="D80" s="12">
         <f>'Tong quan'!$B$3+(C80-1)</f>
-        <v>#VALUE!</v>
+        <v>46269</v>
       </c>
       <c r="E80" s="4" t="s">
         <v>359</v>
@@ -6361,7 +6362,7 @@
         <v>361</v>
       </c>
       <c r="H80" s="3" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="I80" s="3"/>
       <c r="J80" s="4"/>
@@ -6373,7 +6374,7 @@
         <v>91</v>
       </c>
       <c r="N80" s="3" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="O80" s="3"/>
     </row>
@@ -6387,9 +6388,9 @@
       <c r="C81" s="3">
         <v>80</v>
       </c>
-      <c r="D81" s="12" t="e">
+      <c r="D81" s="12">
         <f>'Tong quan'!$B$3+(C81-1)</f>
-        <v>#VALUE!</v>
+        <v>46270</v>
       </c>
       <c r="E81" s="4" t="s">
         <v>363</v>
@@ -6401,7 +6402,7 @@
         <v>364</v>
       </c>
       <c r="H81" s="3" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="I81" s="3"/>
       <c r="J81" s="4"/>
@@ -6413,7 +6414,7 @@
         <v>366</v>
       </c>
       <c r="N81" s="3" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="O81" s="3"/>
     </row>
@@ -6427,9 +6428,9 @@
       <c r="C82" s="3">
         <v>81</v>
       </c>
-      <c r="D82" s="12" t="e">
+      <c r="D82" s="12">
         <f>'Tong quan'!$B$3+(C82-1)</f>
-        <v>#VALUE!</v>
+        <v>46271</v>
       </c>
       <c r="E82" s="4" t="s">
         <v>367</v>
@@ -6441,7 +6442,7 @@
         <v>368</v>
       </c>
       <c r="H82" s="3" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="I82" s="3"/>
       <c r="J82" s="4"/>
@@ -6453,7 +6454,7 @@
         <v>91</v>
       </c>
       <c r="N82" s="3" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="O82" s="3"/>
     </row>
@@ -6467,9 +6468,9 @@
       <c r="C83" s="3">
         <v>82</v>
       </c>
-      <c r="D83" s="12" t="e">
+      <c r="D83" s="12">
         <f>'Tong quan'!$B$3+(C83-1)</f>
-        <v>#VALUE!</v>
+        <v>46272</v>
       </c>
       <c r="E83" s="4" t="s">
         <v>370</v>
@@ -6481,7 +6482,7 @@
         <v>371</v>
       </c>
       <c r="H83" s="3" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="I83" s="3"/>
       <c r="J83" s="4"/>
@@ -6493,7 +6494,7 @@
         <v>97</v>
       </c>
       <c r="N83" s="3" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="O83" s="3"/>
     </row>
@@ -6507,9 +6508,9 @@
       <c r="C84" s="3">
         <v>83</v>
       </c>
-      <c r="D84" s="12" t="e">
+      <c r="D84" s="12">
         <f>'Tong quan'!$B$3+(C84-1)</f>
-        <v>#VALUE!</v>
+        <v>46273</v>
       </c>
       <c r="E84" s="4" t="s">
         <v>373</v>
@@ -6521,7 +6522,7 @@
         <v>374</v>
       </c>
       <c r="H84" s="3" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="I84" s="3"/>
       <c r="J84" s="4"/>
@@ -6533,7 +6534,7 @@
         <v>97</v>
       </c>
       <c r="N84" s="3" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="O84" s="3"/>
     </row>
@@ -6547,9 +6548,9 @@
       <c r="C85" s="13">
         <v>84</v>
       </c>
-      <c r="D85" s="14" t="e">
+      <c r="D85" s="14">
         <f>'Tong quan'!$B$3+(C85-1)</f>
-        <v>#VALUE!</v>
+        <v>46274</v>
       </c>
       <c r="E85" s="15" t="s">
         <v>376</v>
@@ -6561,7 +6562,7 @@
         <v>377</v>
       </c>
       <c r="H85" s="13" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="I85" s="13"/>
       <c r="J85" s="15"/>
@@ -6573,7 +6574,7 @@
         <v>97</v>
       </c>
       <c r="N85" s="13" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="O85" s="13"/>
     </row>
@@ -6610,10 +6611,10 @@
   <sheetData>
     <row r="1" ht="27.6" spans="1:8">
       <c r="A1" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>379</v>
@@ -6631,7 +6632,7 @@
         <v>383</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="2" ht="26.4" spans="1:8">
@@ -6639,7 +6640,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C2" s="4" t="s">
         <v>384</v>
@@ -6653,7 +6654,7 @@
         <v>Chua dat</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G2" s="11">
         <f>COUNTIFS('Theo doi hang ngay'!N2:N8,"Hoan thanh")/7</f>
@@ -6666,7 +6667,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>385</v>
@@ -6680,7 +6681,7 @@
         <v>Chua dat</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G3" s="11">
         <f>COUNTIFS('Theo doi hang ngay'!N9:N15,"Hoan thanh")/7</f>
@@ -6693,7 +6694,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>386</v>
@@ -6707,7 +6708,7 @@
         <v>Chua dat</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G4" s="11">
         <f>COUNTIFS('Theo doi hang ngay'!N16:N22,"Hoan thanh")/7</f>
@@ -6720,7 +6721,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>387</v>
@@ -6734,7 +6735,7 @@
         <v>Chua dat</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G5" s="11">
         <f>COUNTIFS('Theo doi hang ngay'!N23:N29,"Hoan thanh")/7</f>
@@ -6747,7 +6748,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C6" s="4" t="s">
         <v>388</v>
@@ -6761,7 +6762,7 @@
         <v>Chua dat</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G6" s="11">
         <f>COUNTIFS('Theo doi hang ngay'!N30:N36,"Hoan thanh")/7</f>
@@ -6774,7 +6775,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C7" s="4" t="s">
         <v>389</v>
@@ -6788,7 +6789,7 @@
         <v>Chua dat</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G7" s="11">
         <f>COUNTIFS('Theo doi hang ngay'!N37:N43,"Hoan thanh")/7</f>
@@ -6801,7 +6802,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C8" s="4" t="s">
         <v>390</v>
@@ -6815,7 +6816,7 @@
         <v>Chua dat</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G8" s="11">
         <f>COUNTIFS('Theo doi hang ngay'!N44:N50,"Hoan thanh")/7</f>
@@ -6828,7 +6829,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C9" s="4" t="s">
         <v>391</v>
@@ -6842,7 +6843,7 @@
         <v>Chua dat</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G9" s="11">
         <f>COUNTIFS('Theo doi hang ngay'!N51:N57,"Hoan thanh")/7</f>
@@ -6855,7 +6856,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C10" s="4" t="s">
         <v>392</v>
@@ -6869,7 +6870,7 @@
         <v>Chua dat</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G10" s="11">
         <f>COUNTIFS('Theo doi hang ngay'!N58:N64,"Hoan thanh")/7</f>
@@ -6882,7 +6883,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C11" s="4" t="s">
         <v>393</v>
@@ -6896,7 +6897,7 @@
         <v>Chua dat</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G11" s="11">
         <f>COUNTIFS('Theo doi hang ngay'!N65:N71,"Hoan thanh")/7</f>
@@ -6909,7 +6910,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C12" s="4" t="s">
         <v>394</v>
@@ -6923,7 +6924,7 @@
         <v>Chua dat</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G12" s="11">
         <f>COUNTIFS('Theo doi hang ngay'!N72:N78,"Hoan thanh")/7</f>
@@ -6936,7 +6937,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C13" s="4" t="s">
         <v>395</v>
@@ -6950,7 +6951,7 @@
         <v>Chua dat</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G13" s="11">
         <f>COUNTIFS('Theo doi hang ngay'!N79:N85,"Hoan thanh")/7</f>
@@ -6982,7 +6983,7 @@
   <sheetData>
     <row r="1" ht="15.6" spans="1:8">
       <c r="A1" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>396</v>
@@ -6991,7 +6992,7 @@
         <v>397</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F1" s="6" t="s">
         <v>398</v>
@@ -6999,38 +7000,38 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B2" s="4" t="s">
         <v>399</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="D2" s="4"/>
       <c r="F2" s="7" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G2" s="7" t="s">
         <v>400</v>
       </c>
       <c r="H2" s="7" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>261</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="D3" s="4"/>
       <c r="F3" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G3" s="9" t="str">
         <f>COUNTIFS($A$2:$A$21,F3,$C$2:$C$21,"Hoan thanh")&amp;"/"&amp;COUNTIF($A$2:$A$21,F3)</f>
@@ -7043,17 +7044,17 @@
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>401</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="D4" s="4"/>
       <c r="F4" s="8" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G4" s="9" t="str">
         <f>COUNTIFS($A$2:$A$21,F4,$C$2:$C$21,"Hoan thanh")&amp;"/"&amp;COUNTIF($A$2:$A$21,F4)</f>
@@ -7066,17 +7067,17 @@
     </row>
     <row r="5" spans="1:8">
       <c r="A5" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B5" s="4" t="s">
         <v>402</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="D5" s="4"/>
       <c r="F5" s="8" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G5" s="9" t="str">
         <f>COUNTIFS($A$2:$A$21,F5,$C$2:$C$21,"Hoan thanh")&amp;"/"&amp;COUNTIF($A$2:$A$21,F5)</f>
@@ -7089,193 +7090,193 @@
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B6" s="4" t="s">
         <v>403</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="D6" s="4"/>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B7" s="4" t="s">
         <v>404</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="D7" s="4"/>
     </row>
     <row r="8" spans="1:8">
       <c r="A8" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B8" s="4" t="s">
         <v>405</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="D8" s="4"/>
     </row>
     <row r="9" spans="1:8">
       <c r="A9" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B9" s="4" t="s">
         <v>406</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="D9" s="4"/>
     </row>
     <row r="10" spans="1:8">
       <c r="A10" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B10" s="4" t="s">
         <v>407</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="D10" s="4"/>
     </row>
     <row r="11" spans="1:8">
       <c r="A11" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B11" s="4" t="s">
         <v>408</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="D11" s="4"/>
     </row>
     <row r="12" spans="1:8">
       <c r="A12" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B12" s="4" t="s">
         <v>409</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="D12" s="4"/>
     </row>
     <row r="13" spans="1:8">
       <c r="A13" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B13" s="4" t="s">
         <v>410</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="D13" s="4"/>
     </row>
     <row r="14" spans="1:8">
       <c r="A14" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B14" s="4" t="s">
         <v>411</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="D14" s="4"/>
     </row>
     <row r="15" spans="1:8">
       <c r="A15" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B15" s="4" t="s">
         <v>405</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="D15" s="4"/>
     </row>
     <row r="16" spans="1:8">
       <c r="A16" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B16" s="4" t="s">
         <v>412</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="D16" s="4"/>
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B17" s="4" t="s">
         <v>413</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="D17" s="4"/>
     </row>
     <row r="18" spans="1:4">
       <c r="A18" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B18" s="4" t="s">
         <v>414</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="D18" s="4"/>
     </row>
     <row r="19" spans="1:4">
       <c r="A19" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B19" s="4" t="s">
         <v>415</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="D19" s="4"/>
     </row>
     <row r="20" spans="1:4">
       <c r="A20" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B20" s="4" t="s">
         <v>416</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="D20" s="4"/>
     </row>
     <row r="21" spans="1:4">
       <c r="A21" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B21" s="4" t="s">
         <v>405</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="D21" s="4"/>
     </row>

--- a/Blockchain_Intern_Tracker.xlsx
+++ b/Blockchain_Intern_Tracker.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="854" uniqueCount="449">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="855" uniqueCount="450">
   <si>
     <t>BANG THEO DOI TIEN DO - LO TRINH 12 TUAN BLOCKCHAIN DEVELOPER INTERN (RUST / SOLANA)</t>
   </si>
@@ -273,7 +273,7 @@
     <t>Contains Duplicate</t>
   </si>
   <si>
-    <t>su dung cac keyword co san</t>
+    <t>su dung insert trong HashSet</t>
   </si>
   <si>
     <t>Merkle Tree: cau truc, Merkle proof</t>
@@ -289,6 +289,9 @@
   </si>
   <si>
     <t>Valid Anagram</t>
+  </si>
+  <si>
+    <t>su dung sort hay vi sort_unstable</t>
   </si>
   <si>
     <t>Public-key cryptography, digital signature</t>
@@ -2767,7 +2770,7 @@
       </c>
       <c r="E15" s="11">
         <f>COUNTIFS('Theo doi hang ngay'!N2:N8,"Hoan thanh")/7</f>
-        <v>0.285714285714286</v>
+        <v>0.428571428571429</v>
       </c>
     </row>
     <row r="16" ht="26.4" spans="1:8">
@@ -2998,7 +3001,7 @@
       </c>
       <c r="B30" s="20">
         <f>COUNTIF('Theo doi hang ngay'!N2:N85,"Hoan thanh")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -3007,7 +3010,7 @@
       </c>
       <c r="B31" s="20">
         <f>COUNTIF('Theo doi hang ngay'!N2:N85,"Dang lam")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -3025,7 +3028,7 @@
       </c>
       <c r="B33" s="21">
         <f>COUNTIF('Theo doi hang ngay'!N2:N85,"Hoan thanh")/84</f>
-        <v>0.0238095238095238</v>
+        <v>0.0357142857142857</v>
       </c>
     </row>
     <row r="35" ht="15.6" spans="1:3">
@@ -3312,9 +3315,11 @@
         <v>74</v>
       </c>
       <c r="N4" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="O4" s="3"/>
+        <v>71</v>
+      </c>
+      <c r="O4" s="3" t="s">
+        <v>86</v>
+      </c>
     </row>
     <row r="5" ht="26.4" spans="1:15">
       <c r="A5" s="3">
@@ -3331,28 +3336,28 @@
         <v>46194</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I5" s="3"/>
       <c r="J5" s="4"/>
       <c r="K5" s="3"/>
       <c r="L5" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="N5" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="O5" s="3"/>
     </row>
@@ -3371,28 +3376,28 @@
         <v>46195</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I6" s="3"/>
       <c r="J6" s="4"/>
       <c r="K6" s="3"/>
       <c r="L6" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="N6" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="O6" s="3"/>
     </row>
@@ -3411,28 +3416,28 @@
         <v>46196</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I7" s="3"/>
       <c r="J7" s="4"/>
       <c r="K7" s="3"/>
       <c r="L7" s="3" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="N7" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="O7" s="3"/>
     </row>
@@ -3451,28 +3456,28 @@
         <v>46197</v>
       </c>
       <c r="E8" s="15" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F8" s="15" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="G8" s="15" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H8" s="13" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I8" s="13"/>
       <c r="J8" s="15"/>
       <c r="K8" s="13"/>
       <c r="L8" s="13" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="M8" s="13" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="N8" s="13" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="O8" s="13"/>
     </row>
@@ -3491,16 +3496,16 @@
         <v>46198</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I9" s="3"/>
       <c r="J9" s="4"/>
@@ -3508,13 +3513,13 @@
         <v>18</v>
       </c>
       <c r="L9" s="3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="M9" s="3" t="s">
         <v>74</v>
       </c>
       <c r="N9" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="O9" s="3"/>
     </row>
@@ -3533,28 +3538,28 @@
         <v>46199</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I10" s="3"/>
       <c r="J10" s="4"/>
       <c r="K10" s="3"/>
       <c r="L10" s="3" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="M10" s="3" t="s">
         <v>74</v>
       </c>
       <c r="N10" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="O10" s="3"/>
     </row>
@@ -3573,28 +3578,28 @@
         <v>46200</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I11" s="3"/>
       <c r="J11" s="4"/>
       <c r="K11" s="3"/>
       <c r="L11" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="N11" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="O11" s="3"/>
     </row>
@@ -3613,28 +3618,28 @@
         <v>46201</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I12" s="3"/>
       <c r="J12" s="4"/>
       <c r="K12" s="3"/>
       <c r="L12" s="3" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="N12" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="O12" s="3"/>
     </row>
@@ -3653,28 +3658,28 @@
         <v>46202</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I13" s="3"/>
       <c r="J13" s="4"/>
       <c r="K13" s="3"/>
       <c r="L13" s="3" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="M13" s="3" t="s">
         <v>74</v>
       </c>
       <c r="N13" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="O13" s="3"/>
     </row>
@@ -3693,28 +3698,28 @@
         <v>46203</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I14" s="3"/>
       <c r="J14" s="4"/>
       <c r="K14" s="3"/>
       <c r="L14" s="3" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="N14" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="O14" s="3"/>
     </row>
@@ -3733,28 +3738,28 @@
         <v>46204</v>
       </c>
       <c r="E15" s="15" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F15" s="15" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="G15" s="15" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H15" s="13" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I15" s="13"/>
       <c r="J15" s="15"/>
       <c r="K15" s="13"/>
       <c r="L15" s="13" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="M15" s="13" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="N15" s="13" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="O15" s="13"/>
     </row>
@@ -3773,16 +3778,16 @@
         <v>46205</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I16" s="3"/>
       <c r="J16" s="4"/>
@@ -3790,13 +3795,13 @@
         <v>20</v>
       </c>
       <c r="L16" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="M16" s="3" t="s">
         <v>74</v>
       </c>
       <c r="N16" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="O16" s="3"/>
     </row>
@@ -3815,28 +3820,28 @@
         <v>46206</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I17" s="3"/>
       <c r="J17" s="4"/>
       <c r="K17" s="3"/>
       <c r="L17" s="3" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="M17" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="N17" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="O17" s="3"/>
     </row>
@@ -3855,28 +3860,28 @@
         <v>46207</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="G18" s="4" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I18" s="3"/>
       <c r="J18" s="4"/>
       <c r="K18" s="3"/>
       <c r="L18" s="3" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="N18" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="O18" s="3"/>
     </row>
@@ -3895,28 +3900,28 @@
         <v>46208</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="G19" s="4" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I19" s="3"/>
       <c r="J19" s="4"/>
       <c r="K19" s="3"/>
       <c r="L19" s="3" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="M19" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="N19" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="O19" s="3"/>
     </row>
@@ -3935,28 +3940,28 @@
         <v>46209</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="G20" s="4" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I20" s="3"/>
       <c r="J20" s="4"/>
       <c r="K20" s="3"/>
       <c r="L20" s="3" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="M20" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="N20" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="O20" s="3"/>
     </row>
@@ -3975,28 +3980,28 @@
         <v>46210</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="G21" s="4" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I21" s="3"/>
       <c r="J21" s="4"/>
       <c r="K21" s="3"/>
       <c r="L21" s="3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="M21" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="N21" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="O21" s="3"/>
     </row>
@@ -4015,28 +4020,28 @@
         <v>46211</v>
       </c>
       <c r="E22" s="15" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F22" s="15" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="G22" s="15" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="H22" s="13" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I22" s="13"/>
       <c r="J22" s="15"/>
       <c r="K22" s="13"/>
       <c r="L22" s="13" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="M22" s="13" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N22" s="13" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="O22" s="13"/>
     </row>
@@ -4055,16 +4060,16 @@
         <v>46212</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="G23" s="4" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I23" s="3"/>
       <c r="J23" s="4"/>
@@ -4078,7 +4083,7 @@
         <v>74</v>
       </c>
       <c r="N23" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="O23" s="3"/>
     </row>
@@ -4097,28 +4102,28 @@
         <v>46213</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="G24" s="4" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I24" s="3"/>
       <c r="J24" s="4"/>
       <c r="K24" s="3"/>
       <c r="L24" s="3" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="M24" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="N24" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="O24" s="3"/>
     </row>
@@ -4137,28 +4142,28 @@
         <v>46214</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="G25" s="4" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I25" s="3"/>
       <c r="J25" s="4"/>
       <c r="K25" s="3"/>
       <c r="L25" s="3" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="M25" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="N25" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="O25" s="3"/>
     </row>
@@ -4177,28 +4182,28 @@
         <v>46215</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="G26" s="4" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I26" s="3"/>
       <c r="J26" s="4"/>
       <c r="K26" s="3"/>
       <c r="L26" s="3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="M26" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="N26" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="O26" s="3"/>
     </row>
@@ -4217,28 +4222,28 @@
         <v>46216</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="G27" s="4" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I27" s="3"/>
       <c r="J27" s="4"/>
       <c r="K27" s="3"/>
       <c r="L27" s="3" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="M27" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="N27" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="O27" s="3"/>
     </row>
@@ -4257,28 +4262,28 @@
         <v>46217</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="G28" s="4" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I28" s="3"/>
       <c r="J28" s="4"/>
       <c r="K28" s="3"/>
       <c r="L28" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="M28" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="N28" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="O28" s="3"/>
     </row>
@@ -4297,28 +4302,28 @@
         <v>46218</v>
       </c>
       <c r="E29" s="15" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F29" s="15" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="G29" s="15" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H29" s="13" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I29" s="13"/>
       <c r="J29" s="15"/>
       <c r="K29" s="13"/>
       <c r="L29" s="13" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="M29" s="13" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N29" s="13" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="O29" s="13"/>
     </row>
@@ -4337,16 +4342,16 @@
         <v>46219</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="G30" s="4" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I30" s="3"/>
       <c r="J30" s="4"/>
@@ -4354,13 +4359,13 @@
         <v>24</v>
       </c>
       <c r="L30" s="3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="M30" s="3" t="s">
         <v>74</v>
       </c>
       <c r="N30" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="O30" s="3"/>
     </row>
@@ -4379,28 +4384,28 @@
         <v>46220</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="F31" s="4" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="G31" s="4" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I31" s="3"/>
       <c r="J31" s="4"/>
       <c r="K31" s="3"/>
       <c r="L31" s="3" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="M31" s="3" t="s">
         <v>74</v>
       </c>
       <c r="N31" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="O31" s="3"/>
     </row>
@@ -4419,28 +4424,28 @@
         <v>46221</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="G32" s="4" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I32" s="3"/>
       <c r="J32" s="4"/>
       <c r="K32" s="3"/>
       <c r="L32" s="3" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="M32" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="N32" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="O32" s="3"/>
     </row>
@@ -4459,28 +4464,28 @@
         <v>46222</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F33" s="4" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="G33" s="4" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I33" s="3"/>
       <c r="J33" s="4"/>
       <c r="K33" s="3"/>
       <c r="L33" s="3" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="M33" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="N33" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="O33" s="3"/>
     </row>
@@ -4499,28 +4504,28 @@
         <v>46223</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F34" s="4" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="G34" s="4" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I34" s="3"/>
       <c r="J34" s="4"/>
       <c r="K34" s="3"/>
       <c r="L34" s="3" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="M34" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="N34" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="O34" s="3"/>
     </row>
@@ -4539,28 +4544,28 @@
         <v>46224</v>
       </c>
       <c r="E35" s="4" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F35" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="G35" s="4" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I35" s="3"/>
       <c r="J35" s="4"/>
       <c r="K35" s="3"/>
       <c r="L35" s="3" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="M35" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="N35" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="O35" s="3"/>
     </row>
@@ -4579,28 +4584,28 @@
         <v>46225</v>
       </c>
       <c r="E36" s="15" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F36" s="15" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="G36" s="15" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="H36" s="13" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I36" s="13"/>
       <c r="J36" s="15"/>
       <c r="K36" s="13"/>
       <c r="L36" s="13" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="M36" s="13" t="s">
         <v>74</v>
       </c>
       <c r="N36" s="13" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="O36" s="13"/>
     </row>
@@ -4619,16 +4624,16 @@
         <v>46226</v>
       </c>
       <c r="E37" s="4" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F37" s="4" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="G37" s="4" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I37" s="3"/>
       <c r="J37" s="4"/>
@@ -4636,13 +4641,13 @@
         <v>26</v>
       </c>
       <c r="L37" s="3" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="M37" s="3" t="s">
         <v>74</v>
       </c>
       <c r="N37" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="O37" s="3"/>
     </row>
@@ -4661,28 +4666,28 @@
         <v>46227</v>
       </c>
       <c r="E38" s="4" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F38" s="4" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="G38" s="4" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I38" s="3"/>
       <c r="J38" s="4"/>
       <c r="K38" s="3"/>
       <c r="L38" s="3" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="M38" s="3" t="s">
         <v>74</v>
       </c>
       <c r="N38" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="O38" s="3"/>
     </row>
@@ -4701,28 +4706,28 @@
         <v>46228</v>
       </c>
       <c r="E39" s="4" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="F39" s="4" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="G39" s="4" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I39" s="3"/>
       <c r="J39" s="4"/>
       <c r="K39" s="3"/>
       <c r="L39" s="3" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="M39" s="3" t="s">
         <v>74</v>
       </c>
       <c r="N39" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="O39" s="3"/>
     </row>
@@ -4741,28 +4746,28 @@
         <v>46229</v>
       </c>
       <c r="E40" s="4" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="F40" s="4" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G40" s="4" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I40" s="3"/>
       <c r="J40" s="4"/>
       <c r="K40" s="3"/>
       <c r="L40" s="3" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="M40" s="3" t="s">
         <v>74</v>
       </c>
       <c r="N40" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="O40" s="3"/>
     </row>
@@ -4781,28 +4786,28 @@
         <v>46230</v>
       </c>
       <c r="E41" s="4" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F41" s="4" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="G41" s="4" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I41" s="3"/>
       <c r="J41" s="4"/>
       <c r="K41" s="3"/>
       <c r="L41" s="3" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="M41" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="N41" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="O41" s="3"/>
     </row>
@@ -4821,28 +4826,28 @@
         <v>46231</v>
       </c>
       <c r="E42" s="4" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F42" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="G42" s="4" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I42" s="3"/>
       <c r="J42" s="4"/>
       <c r="K42" s="3"/>
       <c r="L42" s="3" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="M42" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="N42" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="O42" s="3"/>
     </row>
@@ -4861,28 +4866,28 @@
         <v>46232</v>
       </c>
       <c r="E43" s="15" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F43" s="15" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="G43" s="15" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="H43" s="13" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I43" s="13"/>
       <c r="J43" s="15"/>
       <c r="K43" s="13"/>
       <c r="L43" s="13" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="M43" s="13" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="N43" s="13" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="O43" s="13"/>
     </row>
@@ -4901,16 +4906,16 @@
         <v>46233</v>
       </c>
       <c r="E44" s="4" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F44" s="4" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="G44" s="4" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="H44" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I44" s="3"/>
       <c r="J44" s="4"/>
@@ -4918,13 +4923,13 @@
         <v>28</v>
       </c>
       <c r="L44" s="3" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="M44" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="N44" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="O44" s="3"/>
     </row>
@@ -4943,28 +4948,28 @@
         <v>46234</v>
       </c>
       <c r="E45" s="4" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="F45" s="4" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="G45" s="4" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I45" s="3"/>
       <c r="J45" s="4"/>
       <c r="K45" s="3"/>
       <c r="L45" s="3" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="M45" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="N45" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="O45" s="3"/>
     </row>
@@ -4983,28 +4988,28 @@
         <v>46235</v>
       </c>
       <c r="E46" s="4" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="F46" s="4" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="G46" s="4" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I46" s="3"/>
       <c r="J46" s="4"/>
       <c r="K46" s="3"/>
       <c r="L46" s="3" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="M46" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="N46" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="O46" s="3"/>
     </row>
@@ -5023,28 +5028,28 @@
         <v>46236</v>
       </c>
       <c r="E47" s="4" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="F47" s="4" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="G47" s="4" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="H47" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I47" s="3"/>
       <c r="J47" s="4"/>
       <c r="K47" s="3"/>
       <c r="L47" s="3" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="M47" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="N47" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="O47" s="3"/>
     </row>
@@ -5063,28 +5068,28 @@
         <v>46237</v>
       </c>
       <c r="E48" s="4" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="F48" s="4" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="G48" s="4" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="H48" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I48" s="3"/>
       <c r="J48" s="4"/>
       <c r="K48" s="3"/>
       <c r="L48" s="3" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="M48" s="3" t="s">
         <v>74</v>
       </c>
       <c r="N48" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="O48" s="3"/>
     </row>
@@ -5103,28 +5108,28 @@
         <v>46238</v>
       </c>
       <c r="E49" s="4" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="F49" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="G49" s="4" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="H49" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I49" s="3"/>
       <c r="J49" s="4"/>
       <c r="K49" s="3"/>
       <c r="L49" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="M49" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="N49" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="O49" s="3"/>
     </row>
@@ -5143,28 +5148,28 @@
         <v>46239</v>
       </c>
       <c r="E50" s="15" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="F50" s="15" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="G50" s="15" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="H50" s="13" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I50" s="13"/>
       <c r="J50" s="15"/>
       <c r="K50" s="13"/>
       <c r="L50" s="13" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="M50" s="13" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="N50" s="13" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="O50" s="13"/>
     </row>
@@ -5183,16 +5188,16 @@
         <v>46240</v>
       </c>
       <c r="E51" s="4" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="F51" s="4" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="G51" s="4" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I51" s="3"/>
       <c r="J51" s="4"/>
@@ -5200,13 +5205,13 @@
         <v>30</v>
       </c>
       <c r="L51" s="3" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="M51" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="N51" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="O51" s="3"/>
     </row>
@@ -5225,28 +5230,28 @@
         <v>46241</v>
       </c>
       <c r="E52" s="4" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="F52" s="4" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="G52" s="4" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I52" s="3"/>
       <c r="J52" s="4"/>
       <c r="K52" s="3"/>
       <c r="L52" s="3" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="M52" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="N52" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="O52" s="3"/>
     </row>
@@ -5265,28 +5270,28 @@
         <v>46242</v>
       </c>
       <c r="E53" s="4" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="F53" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="G53" s="4" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I53" s="3"/>
       <c r="J53" s="4"/>
       <c r="K53" s="3"/>
       <c r="L53" s="3" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="M53" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="N53" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="O53" s="3"/>
     </row>
@@ -5305,28 +5310,28 @@
         <v>46243</v>
       </c>
       <c r="E54" s="4" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="F54" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="G54" s="4" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H54" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I54" s="3"/>
       <c r="J54" s="4"/>
       <c r="K54" s="3"/>
       <c r="L54" s="3" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="M54" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="N54" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="O54" s="3"/>
     </row>
@@ -5345,28 +5350,28 @@
         <v>46244</v>
       </c>
       <c r="E55" s="4" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="F55" s="4" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="G55" s="4" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I55" s="3"/>
       <c r="J55" s="4"/>
       <c r="K55" s="3"/>
       <c r="L55" s="3" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="M55" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="N55" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="O55" s="3"/>
     </row>
@@ -5385,28 +5390,28 @@
         <v>46245</v>
       </c>
       <c r="E56" s="4" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="F56" s="4" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="G56" s="4" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="H56" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I56" s="3"/>
       <c r="J56" s="4"/>
       <c r="K56" s="3"/>
       <c r="L56" s="3" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="M56" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="N56" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="O56" s="3"/>
     </row>
@@ -5425,28 +5430,28 @@
         <v>46246</v>
       </c>
       <c r="E57" s="15" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="F57" s="15" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="G57" s="15" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="H57" s="13" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I57" s="13"/>
       <c r="J57" s="15"/>
       <c r="K57" s="13"/>
       <c r="L57" s="13" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="M57" s="13" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N57" s="13" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="O57" s="13"/>
     </row>
@@ -5465,16 +5470,16 @@
         <v>46247</v>
       </c>
       <c r="E58" s="4" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F58" s="4" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="G58" s="4" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="H58" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I58" s="3"/>
       <c r="J58" s="4"/>
@@ -5482,13 +5487,13 @@
         <v>32</v>
       </c>
       <c r="L58" s="3" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="M58" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="N58" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="O58" s="3"/>
     </row>
@@ -5507,28 +5512,28 @@
         <v>46248</v>
       </c>
       <c r="E59" s="4" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="F59" s="4" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="G59" s="4" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="H59" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I59" s="3"/>
       <c r="J59" s="4"/>
       <c r="K59" s="3"/>
       <c r="L59" s="3" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="M59" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="N59" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="O59" s="3"/>
     </row>
@@ -5547,28 +5552,28 @@
         <v>46249</v>
       </c>
       <c r="E60" s="4" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="F60" s="4" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="G60" s="4" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H60" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I60" s="3"/>
       <c r="J60" s="4"/>
       <c r="K60" s="3"/>
       <c r="L60" s="3" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="M60" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="N60" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="O60" s="3"/>
     </row>
@@ -5587,28 +5592,28 @@
         <v>46250</v>
       </c>
       <c r="E61" s="4" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="F61" s="4" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="G61" s="4" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="H61" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I61" s="3"/>
       <c r="J61" s="4"/>
       <c r="K61" s="3"/>
       <c r="L61" s="3" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="M61" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="N61" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="O61" s="3"/>
     </row>
@@ -5627,28 +5632,28 @@
         <v>46251</v>
       </c>
       <c r="E62" s="4" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="F62" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="G62" s="4" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="H62" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I62" s="3"/>
       <c r="J62" s="4"/>
       <c r="K62" s="3"/>
       <c r="L62" s="3" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="M62" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="N62" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="O62" s="3"/>
     </row>
@@ -5667,28 +5672,28 @@
         <v>46252</v>
       </c>
       <c r="E63" s="4" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="F63" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="G63" s="4" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H63" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I63" s="3"/>
       <c r="J63" s="4"/>
       <c r="K63" s="3"/>
       <c r="L63" s="3" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="M63" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="N63" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="O63" s="3"/>
     </row>
@@ -5707,28 +5712,28 @@
         <v>46253</v>
       </c>
       <c r="E64" s="15" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="F64" s="15" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="G64" s="15" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H64" s="13" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I64" s="13"/>
       <c r="J64" s="15"/>
       <c r="K64" s="13"/>
       <c r="L64" s="13" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="M64" s="13" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="N64" s="13" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="O64" s="13"/>
     </row>
@@ -5747,16 +5752,16 @@
         <v>46254</v>
       </c>
       <c r="E65" s="4" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="F65" s="4" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="G65" s="4" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="H65" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I65" s="3"/>
       <c r="J65" s="4"/>
@@ -5764,13 +5769,13 @@
         <v>34</v>
       </c>
       <c r="L65" s="3" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="M65" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="N65" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="O65" s="3"/>
     </row>
@@ -5789,28 +5794,28 @@
         <v>46255</v>
       </c>
       <c r="E66" s="4" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="F66" s="4" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="G66" s="4" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H66" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I66" s="3"/>
       <c r="J66" s="4"/>
       <c r="K66" s="3"/>
       <c r="L66" s="3" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="M66" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="N66" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="O66" s="3"/>
     </row>
@@ -5829,28 +5834,28 @@
         <v>46256</v>
       </c>
       <c r="E67" s="4" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="F67" s="4" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="G67" s="4" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="H67" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I67" s="3"/>
       <c r="J67" s="4"/>
       <c r="K67" s="3"/>
       <c r="L67" s="3" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="M67" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="N67" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="O67" s="3"/>
     </row>
@@ -5869,28 +5874,28 @@
         <v>46257</v>
       </c>
       <c r="E68" s="4" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="F68" s="4" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="G68" s="4" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I68" s="3"/>
       <c r="J68" s="4"/>
       <c r="K68" s="3"/>
       <c r="L68" s="3" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="M68" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="N68" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="O68" s="3"/>
     </row>
@@ -5909,28 +5914,28 @@
         <v>46258</v>
       </c>
       <c r="E69" s="4" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="F69" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="G69" s="4" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="H69" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I69" s="3"/>
       <c r="J69" s="4"/>
       <c r="K69" s="3"/>
       <c r="L69" s="3" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="M69" s="3" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N69" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="O69" s="3"/>
     </row>
@@ -5949,28 +5954,28 @@
         <v>46259</v>
       </c>
       <c r="E70" s="4" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="F70" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="G70" s="4" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="H70" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I70" s="3"/>
       <c r="J70" s="4"/>
       <c r="K70" s="3"/>
       <c r="L70" s="3" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="M70" s="3" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N70" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="O70" s="3"/>
     </row>
@@ -5989,28 +5994,28 @@
         <v>46260</v>
       </c>
       <c r="E71" s="15" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="F71" s="15" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="G71" s="15" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="H71" s="13" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I71" s="13"/>
       <c r="J71" s="15"/>
       <c r="K71" s="13"/>
       <c r="L71" s="13" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="M71" s="13" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="N71" s="13" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="O71" s="13"/>
     </row>
@@ -6029,16 +6034,16 @@
         <v>46261</v>
       </c>
       <c r="E72" s="4" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="F72" s="4" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="G72" s="4" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="H72" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I72" s="3"/>
       <c r="J72" s="4"/>
@@ -6046,13 +6051,13 @@
         <v>36</v>
       </c>
       <c r="L72" s="3" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="M72" s="3" t="s">
         <v>74</v>
       </c>
       <c r="N72" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="O72" s="3"/>
     </row>
@@ -6071,28 +6076,28 @@
         <v>46262</v>
       </c>
       <c r="E73" s="4" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="F73" s="4" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="G73" s="4" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="H73" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I73" s="3"/>
       <c r="J73" s="4"/>
       <c r="K73" s="3"/>
       <c r="L73" s="3" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="M73" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="N73" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="O73" s="3"/>
     </row>
@@ -6111,28 +6116,28 @@
         <v>46263</v>
       </c>
       <c r="E74" s="4" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="F74" s="4" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="G74" s="4" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="H74" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I74" s="3"/>
       <c r="J74" s="4"/>
       <c r="K74" s="3"/>
       <c r="L74" s="3" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="M74" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="N74" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="O74" s="3"/>
     </row>
@@ -6151,28 +6156,28 @@
         <v>46264</v>
       </c>
       <c r="E75" s="4" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="F75" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="G75" s="4" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="H75" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I75" s="3"/>
       <c r="J75" s="4"/>
       <c r="K75" s="3"/>
       <c r="L75" s="3" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="M75" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="N75" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="O75" s="3"/>
     </row>
@@ -6191,28 +6196,28 @@
         <v>46265</v>
       </c>
       <c r="E76" s="4" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="F76" s="4" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="G76" s="4" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="H76" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I76" s="3"/>
       <c r="J76" s="4"/>
       <c r="K76" s="3"/>
       <c r="L76" s="3" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="M76" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="N76" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="O76" s="3"/>
     </row>
@@ -6231,28 +6236,28 @@
         <v>46266</v>
       </c>
       <c r="E77" s="4" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="F77" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="G77" s="4" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="H77" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I77" s="3"/>
       <c r="J77" s="4"/>
       <c r="K77" s="3"/>
       <c r="L77" s="3" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="M77" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="N77" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="O77" s="3"/>
     </row>
@@ -6271,28 +6276,28 @@
         <v>46267</v>
       </c>
       <c r="E78" s="15" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="F78" s="15" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="G78" s="15" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="H78" s="13" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I78" s="13"/>
       <c r="J78" s="15"/>
       <c r="K78" s="13"/>
       <c r="L78" s="13" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="M78" s="13" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="N78" s="13" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="O78" s="13"/>
     </row>
@@ -6311,16 +6316,16 @@
         <v>46268</v>
       </c>
       <c r="E79" s="4" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="F79" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="G79" s="4" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="H79" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I79" s="3"/>
       <c r="J79" s="4"/>
@@ -6328,13 +6333,13 @@
         <v>38</v>
       </c>
       <c r="L79" s="3" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="M79" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="N79" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="O79" s="3"/>
     </row>
@@ -6353,28 +6358,28 @@
         <v>46269</v>
       </c>
       <c r="E80" s="4" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="F80" s="4" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="G80" s="4" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="H80" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I80" s="3"/>
       <c r="J80" s="4"/>
       <c r="K80" s="3"/>
       <c r="L80" s="3" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="M80" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="N80" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="O80" s="3"/>
     </row>
@@ -6393,28 +6398,28 @@
         <v>46270</v>
       </c>
       <c r="E81" s="4" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="F81" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="G81" s="4" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="H81" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I81" s="3"/>
       <c r="J81" s="4"/>
       <c r="K81" s="3"/>
       <c r="L81" s="3" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="M81" s="3" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="N81" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="O81" s="3"/>
     </row>
@@ -6433,28 +6438,28 @@
         <v>46271</v>
       </c>
       <c r="E82" s="4" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="F82" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="G82" s="4" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="H82" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I82" s="3"/>
       <c r="J82" s="4"/>
       <c r="K82" s="3"/>
       <c r="L82" s="3" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="M82" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="N82" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="O82" s="3"/>
     </row>
@@ -6473,28 +6478,28 @@
         <v>46272</v>
       </c>
       <c r="E83" s="4" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="F83" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="G83" s="4" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="H83" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I83" s="3"/>
       <c r="J83" s="4"/>
       <c r="K83" s="3"/>
       <c r="L83" s="3" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="M83" s="3" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="N83" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="O83" s="3"/>
     </row>
@@ -6513,28 +6518,28 @@
         <v>46273</v>
       </c>
       <c r="E84" s="4" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="F84" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="G84" s="4" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="H84" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I84" s="3"/>
       <c r="J84" s="4"/>
       <c r="K84" s="3"/>
       <c r="L84" s="3" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="M84" s="3" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="N84" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="O84" s="3"/>
     </row>
@@ -6553,28 +6558,28 @@
         <v>46274</v>
       </c>
       <c r="E85" s="15" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="F85" s="15" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="G85" s="15" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="H85" s="13" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I85" s="13"/>
       <c r="J85" s="15"/>
       <c r="K85" s="13"/>
       <c r="L85" s="13" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="M85" s="13" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="N85" s="13" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="O85" s="13"/>
     </row>
@@ -6617,19 +6622,19 @@
         <v>57</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>62</v>
@@ -6643,7 +6648,7 @@
         <v>15</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="D2" s="3" t="str">
         <f>'Theo doi hang ngay'!H8</f>
@@ -6658,7 +6663,7 @@
       </c>
       <c r="G2" s="11">
         <f>COUNTIFS('Theo doi hang ngay'!N2:N8,"Hoan thanh")/7</f>
-        <v>0.285714285714286</v>
+        <v>0.428571428571429</v>
       </c>
       <c r="H2" s="4"/>
     </row>
@@ -6670,7 +6675,7 @@
         <v>17</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="D3" s="3" t="str">
         <f>'Theo doi hang ngay'!H15</f>
@@ -6697,7 +6702,7 @@
         <v>19</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="D4" s="3" t="str">
         <f>'Theo doi hang ngay'!H22</f>
@@ -6724,7 +6729,7 @@
         <v>21</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="D5" s="3" t="str">
         <f>'Theo doi hang ngay'!H29</f>
@@ -6751,7 +6756,7 @@
         <v>23</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="D6" s="3" t="str">
         <f>'Theo doi hang ngay'!H36</f>
@@ -6778,7 +6783,7 @@
         <v>25</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="D7" s="3" t="str">
         <f>'Theo doi hang ngay'!H43</f>
@@ -6805,7 +6810,7 @@
         <v>27</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="D8" s="3" t="str">
         <f>'Theo doi hang ngay'!H50</f>
@@ -6832,7 +6837,7 @@
         <v>29</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="D9" s="3" t="str">
         <f>'Theo doi hang ngay'!H57</f>
@@ -6859,7 +6864,7 @@
         <v>31</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="D10" s="3" t="str">
         <f>'Theo doi hang ngay'!H64</f>
@@ -6886,7 +6891,7 @@
         <v>33</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="D11" s="3" t="str">
         <f>'Theo doi hang ngay'!H71</f>
@@ -6913,7 +6918,7 @@
         <v>35</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="D12" s="3" t="str">
         <f>'Theo doi hang ngay'!H78</f>
@@ -6940,7 +6945,7 @@
         <v>37</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="D13" s="3" t="str">
         <f>'Theo doi hang ngay'!H85</f>
@@ -6986,16 +6991,16 @@
         <v>46</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>62</v>
       </c>
       <c r="F1" s="6" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -7003,17 +7008,17 @@
         <v>49</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D2" s="4"/>
       <c r="F2" s="7" t="s">
         <v>46</v>
       </c>
       <c r="G2" s="7" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="H2" s="7" t="s">
         <v>48</v>
@@ -7024,10 +7029,10 @@
         <v>49</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D3" s="4"/>
       <c r="F3" s="8" t="s">
@@ -7047,10 +7052,10 @@
         <v>49</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D4" s="4"/>
       <c r="F4" s="8" t="s">
@@ -7070,10 +7075,10 @@
         <v>49</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D5" s="4"/>
       <c r="F5" s="8" t="s">
@@ -7093,10 +7098,10 @@
         <v>49</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D6" s="4"/>
     </row>
@@ -7105,10 +7110,10 @@
         <v>49</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D7" s="4"/>
     </row>
@@ -7117,10 +7122,10 @@
         <v>49</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D8" s="4"/>
     </row>
@@ -7129,10 +7134,10 @@
         <v>50</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D9" s="4"/>
     </row>
@@ -7141,10 +7146,10 @@
         <v>50</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D10" s="4"/>
     </row>
@@ -7153,10 +7158,10 @@
         <v>50</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D11" s="4"/>
     </row>
@@ -7165,10 +7170,10 @@
         <v>50</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D12" s="4"/>
     </row>
@@ -7177,10 +7182,10 @@
         <v>50</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D13" s="4"/>
     </row>
@@ -7189,10 +7194,10 @@
         <v>50</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D14" s="4"/>
     </row>
@@ -7201,10 +7206,10 @@
         <v>50</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D15" s="4"/>
     </row>
@@ -7213,10 +7218,10 @@
         <v>51</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D16" s="4"/>
     </row>
@@ -7225,10 +7230,10 @@
         <v>51</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D17" s="4"/>
     </row>
@@ -7237,10 +7242,10 @@
         <v>51</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D18" s="4"/>
     </row>
@@ -7249,10 +7254,10 @@
         <v>51</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D19" s="4"/>
     </row>
@@ -7261,10 +7266,10 @@
         <v>51</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D20" s="4"/>
     </row>
@@ -7273,10 +7278,10 @@
         <v>51</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D21" s="4"/>
     </row>
@@ -7308,22 +7313,22 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="2" spans="1:7">
@@ -7331,13 +7336,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="E2" s="4"/>
       <c r="G2" s="5" t="str">
@@ -7350,13 +7355,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="C3" s="4" t="s">
+        <v>427</v>
+      </c>
+      <c r="D3" s="3" t="s">
         <v>426</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>425</v>
       </c>
       <c r="E3" s="4"/>
     </row>
@@ -7365,13 +7370,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="E4" s="4"/>
     </row>
@@ -7380,13 +7385,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="E5" s="4"/>
     </row>
@@ -7395,13 +7400,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="E6" s="4"/>
     </row>
@@ -7410,13 +7415,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="E7" s="4"/>
     </row>
@@ -7425,13 +7430,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="E8" s="4"/>
     </row>
@@ -7440,13 +7445,13 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="E9" s="4"/>
     </row>
@@ -7455,13 +7460,13 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="E10" s="4"/>
     </row>
@@ -7470,13 +7475,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="E11" s="4"/>
     </row>
@@ -7485,13 +7490,13 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="E12" s="4"/>
     </row>
@@ -7500,13 +7505,13 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="E13" s="4"/>
     </row>
@@ -7515,13 +7520,13 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="E14" s="4"/>
     </row>
@@ -7530,13 +7535,13 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="E15" s="4"/>
     </row>
@@ -7545,13 +7550,13 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="E16" s="4"/>
     </row>
@@ -7560,13 +7565,13 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="E17" s="4"/>
     </row>
@@ -7575,13 +7580,13 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="E18" s="4"/>
     </row>
@@ -7590,13 +7595,13 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="E19" s="4"/>
     </row>
@@ -7605,13 +7610,13 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="E20" s="4"/>
     </row>
@@ -7620,13 +7625,13 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="E21" s="4"/>
     </row>

--- a/Blockchain_Intern_Tracker.xlsx
+++ b/Blockchain_Intern_Tracker.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="855" uniqueCount="450">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="856" uniqueCount="451">
   <si>
     <t>BANG THEO DOI TIEN DO - LO TRINH 12 TUAN BLOCKCHAIN DEVELOPER INTERN (RUST / SOLANA)</t>
   </si>
@@ -303,43 +303,46 @@
     <t>Dung ed25519-dalek: generate keypair, sign, verify</t>
   </si>
   <si>
+    <t>Group Anagrams</t>
+  </si>
+  <si>
+    <t>Medium</t>
+  </si>
+  <si>
+    <t>nho entry, into_values</t>
+  </si>
+  <si>
+    <t>Consensus: PoW, PoS, BFT (gioi thieu Tower BFT)</t>
+  </si>
+  <si>
+    <t>Ethereum.org - Consensus Mechanisms</t>
+  </si>
+  <si>
+    <t>Code PoW miner tim nonce thoa target</t>
+  </si>
+  <si>
+    <t>Top K Frequent Elements</t>
+  </si>
+  <si>
+    <t>Project ngay: ghep thanh mini blockchain</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>Xay rust-mini-blockchain: block+hash+Merkle+PoW+sign</t>
+  </si>
+  <si>
+    <t>Product of Array Except Self</t>
+  </si>
+  <si>
+    <t>Checkpoint tuan 1</t>
+  </si>
+  <si>
+    <t>Tu quiz + push rust-mini-blockchain len GitHub</t>
+  </si>
+  <si>
     <t>Chua bat dau</t>
-  </si>
-  <si>
-    <t>Group Anagrams</t>
-  </si>
-  <si>
-    <t>Medium</t>
-  </si>
-  <si>
-    <t>Consensus: PoW, PoS, BFT (gioi thieu Tower BFT)</t>
-  </si>
-  <si>
-    <t>Ethereum.org - Consensus Mechanisms</t>
-  </si>
-  <si>
-    <t>Code PoW miner tim nonce thoa target</t>
-  </si>
-  <si>
-    <t>Top K Frequent Elements</t>
-  </si>
-  <si>
-    <t>Project ngay: ghep thanh mini blockchain</t>
-  </si>
-  <si>
-    <t>-</t>
-  </si>
-  <si>
-    <t>Xay rust-mini-blockchain: block+hash+Merkle+PoW+sign</t>
-  </si>
-  <si>
-    <t>Product of Array Except Self</t>
-  </si>
-  <si>
-    <t>Checkpoint tuan 1</t>
-  </si>
-  <si>
-    <t>Tu quiz + push rust-mini-blockchain len GitHub</t>
   </si>
   <si>
     <t>Valid Sudoku</t>
@@ -2711,7 +2714,7 @@
       </c>
       <c r="B9" s="20">
         <f>COUNTIF('Theo doi hang ngay'!H2:H85,"Dang lam")</f>
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -2770,7 +2773,7 @@
       </c>
       <c r="E15" s="11">
         <f>COUNTIFS('Theo doi hang ngay'!N2:N8,"Hoan thanh")/7</f>
-        <v>0.428571428571429</v>
+        <v>0.571428571428571</v>
       </c>
     </row>
     <row r="16" ht="26.4" spans="1:8">
@@ -3001,7 +3004,7 @@
       </c>
       <c r="B30" s="20">
         <f>COUNTIF('Theo doi hang ngay'!N2:N85,"Hoan thanh")</f>
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -3010,7 +3013,7 @@
       </c>
       <c r="B31" s="20">
         <f>COUNTIF('Theo doi hang ngay'!N2:N85,"Dang lam")</f>
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -3028,7 +3031,7 @@
       </c>
       <c r="B33" s="21">
         <f>COUNTIF('Theo doi hang ngay'!N2:N85,"Hoan thanh")/84</f>
-        <v>0.0357142857142857</v>
+        <v>0.0476190476190476</v>
       </c>
     </row>
     <row r="35" ht="15.6" spans="1:3">
@@ -3345,21 +3348,23 @@
         <v>89</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="I5" s="3"/>
       <c r="J5" s="4"/>
       <c r="K5" s="3"/>
       <c r="L5" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="M5" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="M5" s="3" t="s">
+      <c r="N5" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="O5" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="N5" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="O5" s="3"/>
     </row>
     <row r="6" ht="26.4" spans="1:15">
       <c r="A6" s="3">
@@ -3385,7 +3390,7 @@
         <v>95</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="I6" s="3"/>
       <c r="J6" s="4"/>
@@ -3394,10 +3399,10 @@
         <v>96</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="N6" s="3" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="O6" s="3"/>
     </row>
@@ -3425,7 +3430,7 @@
         <v>99</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="I7" s="3"/>
       <c r="J7" s="4"/>
@@ -3434,10 +3439,10 @@
         <v>100</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="N7" s="3" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="O7" s="3"/>
     </row>
@@ -3465,19 +3470,19 @@
         <v>102</v>
       </c>
       <c r="H8" s="13" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="I8" s="13"/>
       <c r="J8" s="15"/>
       <c r="K8" s="13"/>
       <c r="L8" s="13" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="M8" s="13" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="N8" s="13" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="O8" s="13"/>
     </row>
@@ -3496,16 +3501,16 @@
         <v>46198</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="I9" s="3"/>
       <c r="J9" s="4"/>
@@ -3513,13 +3518,13 @@
         <v>18</v>
       </c>
       <c r="L9" s="3" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="M9" s="3" t="s">
         <v>74</v>
       </c>
       <c r="N9" s="3" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="O9" s="3"/>
     </row>
@@ -3538,28 +3543,28 @@
         <v>46199</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="I10" s="3"/>
       <c r="J10" s="4"/>
       <c r="K10" s="3"/>
       <c r="L10" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="M10" s="3" t="s">
         <v>74</v>
       </c>
       <c r="N10" s="3" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="O10" s="3"/>
     </row>
@@ -3578,28 +3583,28 @@
         <v>46200</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="I11" s="3"/>
       <c r="J11" s="4"/>
       <c r="K11" s="3"/>
       <c r="L11" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="N11" s="3" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="O11" s="3"/>
     </row>
@@ -3618,28 +3623,28 @@
         <v>46201</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="I12" s="3"/>
       <c r="J12" s="4"/>
       <c r="K12" s="3"/>
       <c r="L12" s="3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="N12" s="3" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="O12" s="3"/>
     </row>
@@ -3658,28 +3663,28 @@
         <v>46202</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="I13" s="3"/>
       <c r="J13" s="4"/>
       <c r="K13" s="3"/>
       <c r="L13" s="3" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="M13" s="3" t="s">
         <v>74</v>
       </c>
       <c r="N13" s="3" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="O13" s="3"/>
     </row>
@@ -3698,28 +3703,28 @@
         <v>46203</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F14" s="4" t="s">
         <v>98</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="I14" s="3"/>
       <c r="J14" s="4"/>
       <c r="K14" s="3"/>
       <c r="L14" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="N14" s="3" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="O14" s="3"/>
     </row>
@@ -3738,28 +3743,28 @@
         <v>46204</v>
       </c>
       <c r="E15" s="15" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F15" s="15" t="s">
         <v>98</v>
       </c>
       <c r="G15" s="15" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H15" s="13" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="I15" s="13"/>
       <c r="J15" s="15"/>
       <c r="K15" s="13"/>
       <c r="L15" s="13" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="M15" s="13" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="N15" s="13" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="O15" s="13"/>
     </row>
@@ -3778,16 +3783,16 @@
         <v>46205</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="I16" s="3"/>
       <c r="J16" s="4"/>
@@ -3795,13 +3800,13 @@
         <v>20</v>
       </c>
       <c r="L16" s="3" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="M16" s="3" t="s">
         <v>74</v>
       </c>
       <c r="N16" s="3" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="O16" s="3"/>
     </row>
@@ -3820,28 +3825,28 @@
         <v>46206</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="I17" s="3"/>
       <c r="J17" s="4"/>
       <c r="K17" s="3"/>
       <c r="L17" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="M17" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="N17" s="3" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="O17" s="3"/>
     </row>
@@ -3860,28 +3865,28 @@
         <v>46207</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="G18" s="4" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="I18" s="3"/>
       <c r="J18" s="4"/>
       <c r="K18" s="3"/>
       <c r="L18" s="3" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="N18" s="3" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="O18" s="3"/>
     </row>
@@ -3900,28 +3905,28 @@
         <v>46208</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="G19" s="4" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="I19" s="3"/>
       <c r="J19" s="4"/>
       <c r="K19" s="3"/>
       <c r="L19" s="3" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="M19" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="N19" s="3" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="O19" s="3"/>
     </row>
@@ -3940,28 +3945,28 @@
         <v>46209</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="G20" s="4" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="I20" s="3"/>
       <c r="J20" s="4"/>
       <c r="K20" s="3"/>
       <c r="L20" s="3" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="M20" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="N20" s="3" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="O20" s="3"/>
     </row>
@@ -3980,28 +3985,28 @@
         <v>46210</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F21" s="4" t="s">
         <v>98</v>
       </c>
       <c r="G21" s="4" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="I21" s="3"/>
       <c r="J21" s="4"/>
       <c r="K21" s="3"/>
       <c r="L21" s="3" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="M21" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="N21" s="3" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="O21" s="3"/>
     </row>
@@ -4020,28 +4025,28 @@
         <v>46211</v>
       </c>
       <c r="E22" s="15" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F22" s="15" t="s">
         <v>98</v>
       </c>
       <c r="G22" s="15" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H22" s="13" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="I22" s="13"/>
       <c r="J22" s="15"/>
       <c r="K22" s="13"/>
       <c r="L22" s="13" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="M22" s="13" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="N22" s="13" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="O22" s="13"/>
     </row>
@@ -4060,16 +4065,16 @@
         <v>46212</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="G23" s="4" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="I23" s="3"/>
       <c r="J23" s="4"/>
@@ -4083,7 +4088,7 @@
         <v>74</v>
       </c>
       <c r="N23" s="3" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="O23" s="3"/>
     </row>
@@ -4102,28 +4107,28 @@
         <v>46213</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="G24" s="4" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="I24" s="3"/>
       <c r="J24" s="4"/>
       <c r="K24" s="3"/>
       <c r="L24" s="3" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="M24" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="N24" s="3" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="O24" s="3"/>
     </row>
@@ -4142,28 +4147,28 @@
         <v>46214</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="G25" s="4" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="I25" s="3"/>
       <c r="J25" s="4"/>
       <c r="K25" s="3"/>
       <c r="L25" s="3" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="M25" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="N25" s="3" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="O25" s="3"/>
     </row>
@@ -4182,28 +4187,28 @@
         <v>46215</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="G26" s="4" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="I26" s="3"/>
       <c r="J26" s="4"/>
       <c r="K26" s="3"/>
       <c r="L26" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="M26" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="N26" s="3" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="O26" s="3"/>
     </row>
@@ -4222,28 +4227,28 @@
         <v>46216</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="G27" s="4" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="I27" s="3"/>
       <c r="J27" s="4"/>
       <c r="K27" s="3"/>
       <c r="L27" s="3" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="M27" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="N27" s="3" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="O27" s="3"/>
     </row>
@@ -4262,28 +4267,28 @@
         <v>46217</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F28" s="4" t="s">
         <v>98</v>
       </c>
       <c r="G28" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="I28" s="3"/>
       <c r="J28" s="4"/>
       <c r="K28" s="3"/>
       <c r="L28" s="3" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="M28" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="N28" s="3" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="O28" s="3"/>
     </row>
@@ -4302,28 +4307,28 @@
         <v>46218</v>
       </c>
       <c r="E29" s="15" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F29" s="15" t="s">
         <v>98</v>
       </c>
       <c r="G29" s="15" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="H29" s="13" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="I29" s="13"/>
       <c r="J29" s="15"/>
       <c r="K29" s="13"/>
       <c r="L29" s="13" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="M29" s="13" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="N29" s="13" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="O29" s="13"/>
     </row>
@@ -4342,16 +4347,16 @@
         <v>46219</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="G30" s="4" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="I30" s="3"/>
       <c r="J30" s="4"/>
@@ -4359,13 +4364,13 @@
         <v>24</v>
       </c>
       <c r="L30" s="3" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="M30" s="3" t="s">
         <v>74</v>
       </c>
       <c r="N30" s="3" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="O30" s="3"/>
     </row>
@@ -4384,28 +4389,28 @@
         <v>46220</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F31" s="4" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="G31" s="4" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="I31" s="3"/>
       <c r="J31" s="4"/>
       <c r="K31" s="3"/>
       <c r="L31" s="3" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="M31" s="3" t="s">
         <v>74</v>
       </c>
       <c r="N31" s="3" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="O31" s="3"/>
     </row>
@@ -4424,28 +4429,28 @@
         <v>46221</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="G32" s="4" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="I32" s="3"/>
       <c r="J32" s="4"/>
       <c r="K32" s="3"/>
       <c r="L32" s="3" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="M32" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="N32" s="3" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="O32" s="3"/>
     </row>
@@ -4464,28 +4469,28 @@
         <v>46222</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F33" s="4" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="G33" s="4" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="I33" s="3"/>
       <c r="J33" s="4"/>
       <c r="K33" s="3"/>
       <c r="L33" s="3" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="M33" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="N33" s="3" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="O33" s="3"/>
     </row>
@@ -4504,28 +4509,28 @@
         <v>46223</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F34" s="4" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="G34" s="4" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="I34" s="3"/>
       <c r="J34" s="4"/>
       <c r="K34" s="3"/>
       <c r="L34" s="3" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="M34" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="N34" s="3" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="O34" s="3"/>
     </row>
@@ -4544,28 +4549,28 @@
         <v>46224</v>
       </c>
       <c r="E35" s="4" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F35" s="4" t="s">
         <v>98</v>
       </c>
       <c r="G35" s="4" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="I35" s="3"/>
       <c r="J35" s="4"/>
       <c r="K35" s="3"/>
       <c r="L35" s="3" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="M35" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="N35" s="3" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="O35" s="3"/>
     </row>
@@ -4584,28 +4589,28 @@
         <v>46225</v>
       </c>
       <c r="E36" s="15" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F36" s="15" t="s">
         <v>98</v>
       </c>
       <c r="G36" s="15" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H36" s="13" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="I36" s="13"/>
       <c r="J36" s="15"/>
       <c r="K36" s="13"/>
       <c r="L36" s="13" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="M36" s="13" t="s">
         <v>74</v>
       </c>
       <c r="N36" s="13" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="O36" s="13"/>
     </row>
@@ -4624,16 +4629,16 @@
         <v>46226</v>
       </c>
       <c r="E37" s="4" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="F37" s="4" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="G37" s="4" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="I37" s="3"/>
       <c r="J37" s="4"/>
@@ -4641,13 +4646,13 @@
         <v>26</v>
       </c>
       <c r="L37" s="3" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="M37" s="3" t="s">
         <v>74</v>
       </c>
       <c r="N37" s="3" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="O37" s="3"/>
     </row>
@@ -4666,28 +4671,28 @@
         <v>46227</v>
       </c>
       <c r="E38" s="4" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F38" s="4" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="G38" s="4" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="I38" s="3"/>
       <c r="J38" s="4"/>
       <c r="K38" s="3"/>
       <c r="L38" s="3" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="M38" s="3" t="s">
         <v>74</v>
       </c>
       <c r="N38" s="3" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="O38" s="3"/>
     </row>
@@ -4706,28 +4711,28 @@
         <v>46228</v>
       </c>
       <c r="E39" s="4" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F39" s="4" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="G39" s="4" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="I39" s="3"/>
       <c r="J39" s="4"/>
       <c r="K39" s="3"/>
       <c r="L39" s="3" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="M39" s="3" t="s">
         <v>74</v>
       </c>
       <c r="N39" s="3" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="O39" s="3"/>
     </row>
@@ -4746,28 +4751,28 @@
         <v>46229</v>
       </c>
       <c r="E40" s="4" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="F40" s="4" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G40" s="4" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="I40" s="3"/>
       <c r="J40" s="4"/>
       <c r="K40" s="3"/>
       <c r="L40" s="3" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="M40" s="3" t="s">
         <v>74</v>
       </c>
       <c r="N40" s="3" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="O40" s="3"/>
     </row>
@@ -4786,28 +4791,28 @@
         <v>46230</v>
       </c>
       <c r="E41" s="4" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="F41" s="4" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="G41" s="4" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="I41" s="3"/>
       <c r="J41" s="4"/>
       <c r="K41" s="3"/>
       <c r="L41" s="3" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="M41" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="N41" s="3" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="O41" s="3"/>
     </row>
@@ -4826,28 +4831,28 @@
         <v>46231</v>
       </c>
       <c r="E42" s="4" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="F42" s="4" t="s">
         <v>98</v>
       </c>
       <c r="G42" s="4" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="I42" s="3"/>
       <c r="J42" s="4"/>
       <c r="K42" s="3"/>
       <c r="L42" s="3" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="M42" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="N42" s="3" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="O42" s="3"/>
     </row>
@@ -4866,28 +4871,28 @@
         <v>46232</v>
       </c>
       <c r="E43" s="15" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="F43" s="15" t="s">
         <v>98</v>
       </c>
       <c r="G43" s="15" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="H43" s="13" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="I43" s="13"/>
       <c r="J43" s="15"/>
       <c r="K43" s="13"/>
       <c r="L43" s="13" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="M43" s="13" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="N43" s="13" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="O43" s="13"/>
     </row>
@@ -4906,16 +4911,16 @@
         <v>46233</v>
       </c>
       <c r="E44" s="4" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="F44" s="4" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="G44" s="4" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="H44" s="3" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="I44" s="3"/>
       <c r="J44" s="4"/>
@@ -4923,13 +4928,13 @@
         <v>28</v>
       </c>
       <c r="L44" s="3" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="M44" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="N44" s="3" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="O44" s="3"/>
     </row>
@@ -4948,28 +4953,28 @@
         <v>46234</v>
       </c>
       <c r="E45" s="4" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="F45" s="4" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="G45" s="4" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="I45" s="3"/>
       <c r="J45" s="4"/>
       <c r="K45" s="3"/>
       <c r="L45" s="3" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="M45" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="N45" s="3" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="O45" s="3"/>
     </row>
@@ -4988,28 +4993,28 @@
         <v>46235</v>
       </c>
       <c r="E46" s="4" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="F46" s="4" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="G46" s="4" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="I46" s="3"/>
       <c r="J46" s="4"/>
       <c r="K46" s="3"/>
       <c r="L46" s="3" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="M46" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="N46" s="3" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="O46" s="3"/>
     </row>
@@ -5028,28 +5033,28 @@
         <v>46236</v>
       </c>
       <c r="E47" s="4" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="F47" s="4" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="G47" s="4" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="H47" s="3" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="I47" s="3"/>
       <c r="J47" s="4"/>
       <c r="K47" s="3"/>
       <c r="L47" s="3" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="M47" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="N47" s="3" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="O47" s="3"/>
     </row>
@@ -5068,28 +5073,28 @@
         <v>46237</v>
       </c>
       <c r="E48" s="4" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="F48" s="4" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="G48" s="4" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H48" s="3" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="I48" s="3"/>
       <c r="J48" s="4"/>
       <c r="K48" s="3"/>
       <c r="L48" s="3" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="M48" s="3" t="s">
         <v>74</v>
       </c>
       <c r="N48" s="3" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="O48" s="3"/>
     </row>
@@ -5108,28 +5113,28 @@
         <v>46238</v>
       </c>
       <c r="E49" s="4" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="F49" s="4" t="s">
         <v>98</v>
       </c>
       <c r="G49" s="4" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="H49" s="3" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="I49" s="3"/>
       <c r="J49" s="4"/>
       <c r="K49" s="3"/>
       <c r="L49" s="3" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="M49" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="N49" s="3" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="O49" s="3"/>
     </row>
@@ -5148,28 +5153,28 @@
         <v>46239</v>
       </c>
       <c r="E50" s="15" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="F50" s="15" t="s">
         <v>98</v>
       </c>
       <c r="G50" s="15" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H50" s="13" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="I50" s="13"/>
       <c r="J50" s="15"/>
       <c r="K50" s="13"/>
       <c r="L50" s="13" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="M50" s="13" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="N50" s="13" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="O50" s="13"/>
     </row>
@@ -5188,16 +5193,16 @@
         <v>46240</v>
       </c>
       <c r="E51" s="4" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F51" s="4" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="G51" s="4" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="I51" s="3"/>
       <c r="J51" s="4"/>
@@ -5205,13 +5210,13 @@
         <v>30</v>
       </c>
       <c r="L51" s="3" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="M51" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="N51" s="3" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="O51" s="3"/>
     </row>
@@ -5230,28 +5235,28 @@
         <v>46241</v>
       </c>
       <c r="E52" s="4" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="F52" s="4" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="G52" s="4" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="I52" s="3"/>
       <c r="J52" s="4"/>
       <c r="K52" s="3"/>
       <c r="L52" s="3" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="M52" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="N52" s="3" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="O52" s="3"/>
     </row>
@@ -5270,28 +5275,28 @@
         <v>46242</v>
       </c>
       <c r="E53" s="4" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="F53" s="4" t="s">
         <v>98</v>
       </c>
       <c r="G53" s="4" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="I53" s="3"/>
       <c r="J53" s="4"/>
       <c r="K53" s="3"/>
       <c r="L53" s="3" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="M53" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="N53" s="3" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="O53" s="3"/>
     </row>
@@ -5310,28 +5315,28 @@
         <v>46243</v>
       </c>
       <c r="E54" s="4" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="F54" s="4" t="s">
         <v>98</v>
       </c>
       <c r="G54" s="4" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H54" s="3" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="I54" s="3"/>
       <c r="J54" s="4"/>
       <c r="K54" s="3"/>
       <c r="L54" s="3" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="M54" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="N54" s="3" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="O54" s="3"/>
     </row>
@@ -5350,28 +5355,28 @@
         <v>46244</v>
       </c>
       <c r="E55" s="4" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F55" s="4" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="G55" s="4" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="I55" s="3"/>
       <c r="J55" s="4"/>
       <c r="K55" s="3"/>
       <c r="L55" s="3" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="M55" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="N55" s="3" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="O55" s="3"/>
     </row>
@@ -5390,28 +5395,28 @@
         <v>46245</v>
       </c>
       <c r="E56" s="4" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="F56" s="4" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="G56" s="4" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H56" s="3" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="I56" s="3"/>
       <c r="J56" s="4"/>
       <c r="K56" s="3"/>
       <c r="L56" s="3" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="M56" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="N56" s="3" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="O56" s="3"/>
     </row>
@@ -5430,28 +5435,28 @@
         <v>46246</v>
       </c>
       <c r="E57" s="15" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F57" s="15" t="s">
         <v>98</v>
       </c>
       <c r="G57" s="15" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="H57" s="13" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="I57" s="13"/>
       <c r="J57" s="15"/>
       <c r="K57" s="13"/>
       <c r="L57" s="13" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="M57" s="13" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="N57" s="13" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="O57" s="13"/>
     </row>
@@ -5470,16 +5475,16 @@
         <v>46247</v>
       </c>
       <c r="E58" s="4" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="F58" s="4" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="G58" s="4" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="H58" s="3" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="I58" s="3"/>
       <c r="J58" s="4"/>
@@ -5487,13 +5492,13 @@
         <v>32</v>
       </c>
       <c r="L58" s="3" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="M58" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="N58" s="3" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="O58" s="3"/>
     </row>
@@ -5512,28 +5517,28 @@
         <v>46248</v>
       </c>
       <c r="E59" s="4" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="F59" s="4" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="G59" s="4" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="H59" s="3" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="I59" s="3"/>
       <c r="J59" s="4"/>
       <c r="K59" s="3"/>
       <c r="L59" s="3" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="M59" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="N59" s="3" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="O59" s="3"/>
     </row>
@@ -5552,28 +5557,28 @@
         <v>46249</v>
       </c>
       <c r="E60" s="4" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="F60" s="4" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="G60" s="4" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H60" s="3" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="I60" s="3"/>
       <c r="J60" s="4"/>
       <c r="K60" s="3"/>
       <c r="L60" s="3" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="M60" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="N60" s="3" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="O60" s="3"/>
     </row>
@@ -5592,28 +5597,28 @@
         <v>46250</v>
       </c>
       <c r="E61" s="4" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="F61" s="4" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="G61" s="4" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="H61" s="3" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="I61" s="3"/>
       <c r="J61" s="4"/>
       <c r="K61" s="3"/>
       <c r="L61" s="3" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="M61" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="N61" s="3" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="O61" s="3"/>
     </row>
@@ -5632,28 +5637,28 @@
         <v>46251</v>
       </c>
       <c r="E62" s="4" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="F62" s="4" t="s">
         <v>98</v>
       </c>
       <c r="G62" s="4" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="H62" s="3" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="I62" s="3"/>
       <c r="J62" s="4"/>
       <c r="K62" s="3"/>
       <c r="L62" s="3" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="M62" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="N62" s="3" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="O62" s="3"/>
     </row>
@@ -5672,28 +5677,28 @@
         <v>46252</v>
       </c>
       <c r="E63" s="4" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="F63" s="4" t="s">
         <v>98</v>
       </c>
       <c r="G63" s="4" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="H63" s="3" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="I63" s="3"/>
       <c r="J63" s="4"/>
       <c r="K63" s="3"/>
       <c r="L63" s="3" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="M63" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="N63" s="3" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="O63" s="3"/>
     </row>
@@ -5712,28 +5717,28 @@
         <v>46253</v>
       </c>
       <c r="E64" s="15" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="F64" s="15" t="s">
         <v>98</v>
       </c>
       <c r="G64" s="15" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H64" s="13" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="I64" s="13"/>
       <c r="J64" s="15"/>
       <c r="K64" s="13"/>
       <c r="L64" s="13" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="M64" s="13" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="N64" s="13" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="O64" s="13"/>
     </row>
@@ -5752,16 +5757,16 @@
         <v>46254</v>
       </c>
       <c r="E65" s="4" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="F65" s="4" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="G65" s="4" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="H65" s="3" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="I65" s="3"/>
       <c r="J65" s="4"/>
@@ -5769,13 +5774,13 @@
         <v>34</v>
       </c>
       <c r="L65" s="3" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="M65" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="N65" s="3" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="O65" s="3"/>
     </row>
@@ -5794,28 +5799,28 @@
         <v>46255</v>
       </c>
       <c r="E66" s="4" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="F66" s="4" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="G66" s="4" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="H66" s="3" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="I66" s="3"/>
       <c r="J66" s="4"/>
       <c r="K66" s="3"/>
       <c r="L66" s="3" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="M66" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="N66" s="3" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="O66" s="3"/>
     </row>
@@ -5834,28 +5839,28 @@
         <v>46256</v>
       </c>
       <c r="E67" s="4" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="F67" s="4" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="G67" s="4" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="H67" s="3" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="I67" s="3"/>
       <c r="J67" s="4"/>
       <c r="K67" s="3"/>
       <c r="L67" s="3" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="M67" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="N67" s="3" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="O67" s="3"/>
     </row>
@@ -5874,28 +5879,28 @@
         <v>46257</v>
       </c>
       <c r="E68" s="4" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="F68" s="4" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="G68" s="4" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="I68" s="3"/>
       <c r="J68" s="4"/>
       <c r="K68" s="3"/>
       <c r="L68" s="3" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="M68" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="N68" s="3" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="O68" s="3"/>
     </row>
@@ -5914,28 +5919,28 @@
         <v>46258</v>
       </c>
       <c r="E69" s="4" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="F69" s="4" t="s">
         <v>98</v>
       </c>
       <c r="G69" s="4" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="H69" s="3" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="I69" s="3"/>
       <c r="J69" s="4"/>
       <c r="K69" s="3"/>
       <c r="L69" s="3" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="M69" s="3" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="N69" s="3" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="O69" s="3"/>
     </row>
@@ -5954,28 +5959,28 @@
         <v>46259</v>
       </c>
       <c r="E70" s="4" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F70" s="4" t="s">
         <v>98</v>
       </c>
       <c r="G70" s="4" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="H70" s="3" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="I70" s="3"/>
       <c r="J70" s="4"/>
       <c r="K70" s="3"/>
       <c r="L70" s="3" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="M70" s="3" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="N70" s="3" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="O70" s="3"/>
     </row>
@@ -5994,28 +5999,28 @@
         <v>46260</v>
       </c>
       <c r="E71" s="15" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="F71" s="15" t="s">
         <v>98</v>
       </c>
       <c r="G71" s="15" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="H71" s="13" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="I71" s="13"/>
       <c r="J71" s="15"/>
       <c r="K71" s="13"/>
       <c r="L71" s="13" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="M71" s="13" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="N71" s="13" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="O71" s="13"/>
     </row>
@@ -6034,16 +6039,16 @@
         <v>46261</v>
       </c>
       <c r="E72" s="4" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="F72" s="4" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="G72" s="4" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="H72" s="3" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="I72" s="3"/>
       <c r="J72" s="4"/>
@@ -6051,13 +6056,13 @@
         <v>36</v>
       </c>
       <c r="L72" s="3" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="M72" s="3" t="s">
         <v>74</v>
       </c>
       <c r="N72" s="3" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="O72" s="3"/>
     </row>
@@ -6076,28 +6081,28 @@
         <v>46262</v>
       </c>
       <c r="E73" s="4" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="F73" s="4" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="G73" s="4" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="H73" s="3" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="I73" s="3"/>
       <c r="J73" s="4"/>
       <c r="K73" s="3"/>
       <c r="L73" s="3" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="M73" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="N73" s="3" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="O73" s="3"/>
     </row>
@@ -6116,28 +6121,28 @@
         <v>46263</v>
       </c>
       <c r="E74" s="4" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="F74" s="4" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="G74" s="4" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="H74" s="3" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="I74" s="3"/>
       <c r="J74" s="4"/>
       <c r="K74" s="3"/>
       <c r="L74" s="3" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="M74" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="N74" s="3" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="O74" s="3"/>
     </row>
@@ -6156,28 +6161,28 @@
         <v>46264</v>
       </c>
       <c r="E75" s="4" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="F75" s="4" t="s">
         <v>98</v>
       </c>
       <c r="G75" s="4" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="H75" s="3" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="I75" s="3"/>
       <c r="J75" s="4"/>
       <c r="K75" s="3"/>
       <c r="L75" s="3" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="M75" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="N75" s="3" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="O75" s="3"/>
     </row>
@@ -6196,28 +6201,28 @@
         <v>46265</v>
       </c>
       <c r="E76" s="4" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="F76" s="4" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="G76" s="4" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="H76" s="3" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="I76" s="3"/>
       <c r="J76" s="4"/>
       <c r="K76" s="3"/>
       <c r="L76" s="3" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="M76" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="N76" s="3" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="O76" s="3"/>
     </row>
@@ -6236,28 +6241,28 @@
         <v>46266</v>
       </c>
       <c r="E77" s="4" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="F77" s="4" t="s">
         <v>98</v>
       </c>
       <c r="G77" s="4" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="H77" s="3" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="I77" s="3"/>
       <c r="J77" s="4"/>
       <c r="K77" s="3"/>
       <c r="L77" s="3" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="M77" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="N77" s="3" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="O77" s="3"/>
     </row>
@@ -6276,28 +6281,28 @@
         <v>46267</v>
       </c>
       <c r="E78" s="15" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="F78" s="15" t="s">
         <v>98</v>
       </c>
       <c r="G78" s="15" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="H78" s="13" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="I78" s="13"/>
       <c r="J78" s="15"/>
       <c r="K78" s="13"/>
       <c r="L78" s="13" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="M78" s="13" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="N78" s="13" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="O78" s="13"/>
     </row>
@@ -6316,16 +6321,16 @@
         <v>46268</v>
       </c>
       <c r="E79" s="4" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="F79" s="4" t="s">
         <v>98</v>
       </c>
       <c r="G79" s="4" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="H79" s="3" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="I79" s="3"/>
       <c r="J79" s="4"/>
@@ -6333,13 +6338,13 @@
         <v>38</v>
       </c>
       <c r="L79" s="3" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="M79" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="N79" s="3" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="O79" s="3"/>
     </row>
@@ -6358,28 +6363,28 @@
         <v>46269</v>
       </c>
       <c r="E80" s="4" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="F80" s="4" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="G80" s="4" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="H80" s="3" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="I80" s="3"/>
       <c r="J80" s="4"/>
       <c r="K80" s="3"/>
       <c r="L80" s="3" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="M80" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="N80" s="3" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="O80" s="3"/>
     </row>
@@ -6398,28 +6403,28 @@
         <v>46270</v>
       </c>
       <c r="E81" s="4" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="F81" s="4" t="s">
         <v>98</v>
       </c>
       <c r="G81" s="4" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="H81" s="3" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="I81" s="3"/>
       <c r="J81" s="4"/>
       <c r="K81" s="3"/>
       <c r="L81" s="3" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="M81" s="3" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="N81" s="3" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="O81" s="3"/>
     </row>
@@ -6438,28 +6443,28 @@
         <v>46271</v>
       </c>
       <c r="E82" s="4" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="F82" s="4" t="s">
         <v>98</v>
       </c>
       <c r="G82" s="4" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="H82" s="3" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="I82" s="3"/>
       <c r="J82" s="4"/>
       <c r="K82" s="3"/>
       <c r="L82" s="3" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="M82" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="N82" s="3" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="O82" s="3"/>
     </row>
@@ -6478,28 +6483,28 @@
         <v>46272</v>
       </c>
       <c r="E83" s="4" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="F83" s="4" t="s">
         <v>98</v>
       </c>
       <c r="G83" s="4" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="H83" s="3" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="I83" s="3"/>
       <c r="J83" s="4"/>
       <c r="K83" s="3"/>
       <c r="L83" s="3" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="M83" s="3" t="s">
         <v>98</v>
       </c>
       <c r="N83" s="3" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="O83" s="3"/>
     </row>
@@ -6518,28 +6523,28 @@
         <v>46273</v>
       </c>
       <c r="E84" s="4" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="F84" s="4" t="s">
         <v>98</v>
       </c>
       <c r="G84" s="4" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="H84" s="3" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="I84" s="3"/>
       <c r="J84" s="4"/>
       <c r="K84" s="3"/>
       <c r="L84" s="3" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="M84" s="3" t="s">
         <v>98</v>
       </c>
       <c r="N84" s="3" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="O84" s="3"/>
     </row>
@@ -6558,28 +6563,28 @@
         <v>46274</v>
       </c>
       <c r="E85" s="15" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="F85" s="15" t="s">
         <v>98</v>
       </c>
       <c r="G85" s="15" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="H85" s="13" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="I85" s="13"/>
       <c r="J85" s="15"/>
       <c r="K85" s="13"/>
       <c r="L85" s="13" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="M85" s="13" t="s">
         <v>98</v>
       </c>
       <c r="N85" s="13" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="O85" s="13"/>
     </row>
@@ -6622,19 +6627,19 @@
         <v>57</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>62</v>
@@ -6648,7 +6653,7 @@
         <v>15</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="D2" s="3" t="str">
         <f>'Theo doi hang ngay'!H8</f>
@@ -6663,7 +6668,7 @@
       </c>
       <c r="G2" s="11">
         <f>COUNTIFS('Theo doi hang ngay'!N2:N8,"Hoan thanh")/7</f>
-        <v>0.428571428571429</v>
+        <v>0.571428571428571</v>
       </c>
       <c r="H2" s="4"/>
     </row>
@@ -6675,7 +6680,7 @@
         <v>17</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="D3" s="3" t="str">
         <f>'Theo doi hang ngay'!H15</f>
@@ -6702,7 +6707,7 @@
         <v>19</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="D4" s="3" t="str">
         <f>'Theo doi hang ngay'!H22</f>
@@ -6729,7 +6734,7 @@
         <v>21</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="D5" s="3" t="str">
         <f>'Theo doi hang ngay'!H29</f>
@@ -6756,7 +6761,7 @@
         <v>23</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="D6" s="3" t="str">
         <f>'Theo doi hang ngay'!H36</f>
@@ -6783,7 +6788,7 @@
         <v>25</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="D7" s="3" t="str">
         <f>'Theo doi hang ngay'!H43</f>
@@ -6810,7 +6815,7 @@
         <v>27</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="D8" s="3" t="str">
         <f>'Theo doi hang ngay'!H50</f>
@@ -6837,7 +6842,7 @@
         <v>29</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="D9" s="3" t="str">
         <f>'Theo doi hang ngay'!H57</f>
@@ -6864,7 +6869,7 @@
         <v>31</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="D10" s="3" t="str">
         <f>'Theo doi hang ngay'!H64</f>
@@ -6891,7 +6896,7 @@
         <v>33</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="D11" s="3" t="str">
         <f>'Theo doi hang ngay'!H71</f>
@@ -6918,7 +6923,7 @@
         <v>35</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="D12" s="3" t="str">
         <f>'Theo doi hang ngay'!H78</f>
@@ -6945,7 +6950,7 @@
         <v>37</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="D13" s="3" t="str">
         <f>'Theo doi hang ngay'!H85</f>
@@ -6991,16 +6996,16 @@
         <v>46</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>62</v>
       </c>
       <c r="F1" s="6" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -7008,17 +7013,17 @@
         <v>49</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="D2" s="4"/>
       <c r="F2" s="7" t="s">
         <v>46</v>
       </c>
       <c r="G2" s="7" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="H2" s="7" t="s">
         <v>48</v>
@@ -7029,10 +7034,10 @@
         <v>49</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="D3" s="4"/>
       <c r="F3" s="8" t="s">
@@ -7052,10 +7057,10 @@
         <v>49</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="D4" s="4"/>
       <c r="F4" s="8" t="s">
@@ -7075,10 +7080,10 @@
         <v>49</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="D5" s="4"/>
       <c r="F5" s="8" t="s">
@@ -7098,10 +7103,10 @@
         <v>49</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="D6" s="4"/>
     </row>
@@ -7110,10 +7115,10 @@
         <v>49</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="D7" s="4"/>
     </row>
@@ -7122,10 +7127,10 @@
         <v>49</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="D8" s="4"/>
     </row>
@@ -7134,10 +7139,10 @@
         <v>50</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="D9" s="4"/>
     </row>
@@ -7146,10 +7151,10 @@
         <v>50</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="D10" s="4"/>
     </row>
@@ -7158,10 +7163,10 @@
         <v>50</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="D11" s="4"/>
     </row>
@@ -7170,10 +7175,10 @@
         <v>50</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="D12" s="4"/>
     </row>
@@ -7182,10 +7187,10 @@
         <v>50</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="D13" s="4"/>
     </row>
@@ -7194,10 +7199,10 @@
         <v>50</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="D14" s="4"/>
     </row>
@@ -7206,10 +7211,10 @@
         <v>50</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="D15" s="4"/>
     </row>
@@ -7218,10 +7223,10 @@
         <v>51</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="D16" s="4"/>
     </row>
@@ -7230,10 +7235,10 @@
         <v>51</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="D17" s="4"/>
     </row>
@@ -7242,10 +7247,10 @@
         <v>51</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="D18" s="4"/>
     </row>
@@ -7254,10 +7259,10 @@
         <v>51</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="D19" s="4"/>
     </row>
@@ -7266,10 +7271,10 @@
         <v>51</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="D20" s="4"/>
     </row>
@@ -7278,10 +7283,10 @@
         <v>51</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="D21" s="4"/>
     </row>
@@ -7313,22 +7318,22 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="2" spans="1:7">
@@ -7336,13 +7341,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="E2" s="4"/>
       <c r="G2" s="5" t="str">
@@ -7355,13 +7360,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="C3" s="4" t="s">
+        <v>428</v>
+      </c>
+      <c r="D3" s="3" t="s">
         <v>427</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>426</v>
       </c>
       <c r="E3" s="4"/>
     </row>
@@ -7370,13 +7375,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="E4" s="4"/>
     </row>
@@ -7385,13 +7390,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="E5" s="4"/>
     </row>
@@ -7400,13 +7405,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="E6" s="4"/>
     </row>
@@ -7415,13 +7420,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="E7" s="4"/>
     </row>
@@ -7430,13 +7435,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="E8" s="4"/>
     </row>
@@ -7445,13 +7450,13 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="E9" s="4"/>
     </row>
@@ -7460,13 +7465,13 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="E10" s="4"/>
     </row>
@@ -7475,13 +7480,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="E11" s="4"/>
     </row>
@@ -7490,13 +7495,13 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="E12" s="4"/>
     </row>
@@ -7505,13 +7510,13 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="E13" s="4"/>
     </row>
@@ -7520,13 +7525,13 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="E14" s="4"/>
     </row>
@@ -7535,13 +7540,13 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="E15" s="4"/>
     </row>
@@ -7550,13 +7555,13 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="E16" s="4"/>
     </row>
@@ -7565,13 +7570,13 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="E17" s="4"/>
     </row>
@@ -7580,13 +7585,13 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="E18" s="4"/>
     </row>
@@ -7595,13 +7600,13 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="E19" s="4"/>
     </row>
@@ -7610,13 +7615,13 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="E20" s="4"/>
     </row>
@@ -7625,13 +7630,13 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="E21" s="4"/>
     </row>
